--- a/research/traditional_assets/database/data/luxembourg/luxembourg_entertainment.xlsx
+++ b/research/traditional_assets/database/data/luxembourg/luxembourg_entertainment.xlsx
@@ -587,32 +587,38 @@
           <t>Entertainment</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.21</v>
+      </c>
+      <c r="F2">
+        <v>4.23</v>
+      </c>
       <c r="G2">
-        <v>0.1248685594111462</v>
+        <v>0.08724279835390945</v>
       </c>
       <c r="H2">
-        <v>0.01598136263098734</v>
+        <v>-0.04397731064397731</v>
       </c>
       <c r="I2">
-        <v>-0.03786395445810218</v>
+        <v>-0.03178734289845401</v>
       </c>
       <c r="J2">
-        <v>-0.03786395445810218</v>
+        <v>-0.03178734289845401</v>
       </c>
       <c r="K2">
-        <v>-195.1</v>
+        <v>-774.8</v>
       </c>
       <c r="L2">
-        <v>-0.01768555785198883</v>
+        <v>-0.05745004263522781</v>
       </c>
       <c r="M2">
-        <v>109.8</v>
+        <v>61.4</v>
       </c>
       <c r="N2">
-        <v>0.007201133293108423</v>
+        <v>0.001674457164985846</v>
       </c>
       <c r="O2">
-        <v>-0.5627883136852896</v>
+        <v>-0.0792462570986061</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +630,70 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>109.8</v>
+        <v>61.4</v>
       </c>
       <c r="T2">
         <v>1</v>
       </c>
       <c r="U2">
-        <v>2795.6</v>
+        <v>2771</v>
       </c>
       <c r="V2">
-        <v>0.1833468873789973</v>
+        <v>0.07556874273901922</v>
       </c>
       <c r="W2">
-        <v>-0.07951581349853278</v>
+        <v>-0.3538545853123858</v>
       </c>
       <c r="X2">
-        <v>0.1041533624241665</v>
+        <v>0.08742480683182866</v>
       </c>
       <c r="Y2">
-        <v>-0.1836691759226993</v>
-      </c>
-      <c r="Z2">
-        <v>17.72714125020087</v>
-      </c>
-      <c r="AA2">
-        <v>-0.6712196689699502</v>
+        <v>-0.4412793921442145</v>
       </c>
       <c r="AB2">
-        <v>0.1041533624241665</v>
-      </c>
-      <c r="AC2">
-        <v>-0.7753730313941167</v>
+        <v>0.08499991742710145</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1898.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1898.8</v>
       </c>
       <c r="AG2">
-        <v>-2795.6</v>
+        <v>-872.2</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>0.04923329029180085</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>0.4561352935524166</v>
       </c>
       <c r="AJ2">
-        <v>-0.2245101188564086</v>
+        <v>-0.02436557866154138</v>
       </c>
       <c r="AK2">
-        <v>4.613201320132013</v>
+        <v>-0.6266704986348614</v>
       </c>
       <c r="AL2">
-        <v>51</v>
+        <v>59.3</v>
       </c>
       <c r="AM2">
-        <v>23.5</v>
+        <v>-59.2</v>
       </c>
       <c r="AN2">
-        <v>-0</v>
+        <v>-4.956408248499086</v>
       </c>
       <c r="AO2">
-        <v>-8.190196078431372</v>
+        <v>-7.229342327150085</v>
       </c>
       <c r="AP2">
-        <v>7.199587947463301</v>
+        <v>2.276690159227356</v>
       </c>
       <c r="AQ2">
-        <v>-17.77446808510638</v>
+        <v>7.241554054054054</v>
       </c>
     </row>
     <row r="3">
@@ -715,32 +712,38 @@
           <t>Entertainment</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.21</v>
+      </c>
+      <c r="F3">
+        <v>4.23</v>
+      </c>
       <c r="G3">
-        <v>0.1248685594111462</v>
+        <v>0.08724279835390945</v>
       </c>
       <c r="H3">
-        <v>0.01598136263098734</v>
+        <v>-0.04397731064397731</v>
       </c>
       <c r="I3">
-        <v>-0.03786395445810218</v>
+        <v>-0.03178734289845401</v>
       </c>
       <c r="J3">
-        <v>-0.03786395445810218</v>
+        <v>-0.03178734289845401</v>
       </c>
       <c r="K3">
-        <v>-195.1</v>
+        <v>-774.8</v>
       </c>
       <c r="L3">
-        <v>-0.01768555785198883</v>
+        <v>-0.05745004263522781</v>
       </c>
       <c r="M3">
-        <v>109.8</v>
+        <v>61.4</v>
       </c>
       <c r="N3">
-        <v>0.007201133293108423</v>
+        <v>0.001674457164985846</v>
       </c>
       <c r="O3">
-        <v>-0.5627883136852896</v>
+        <v>-0.0792462570986061</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +755,70 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>109.8</v>
+        <v>61.4</v>
       </c>
       <c r="T3">
         <v>1</v>
       </c>
       <c r="U3">
-        <v>2795.6</v>
+        <v>2771</v>
       </c>
       <c r="V3">
-        <v>0.1833468873789973</v>
+        <v>0.07556874273901922</v>
       </c>
       <c r="W3">
-        <v>-0.07951581349853278</v>
+        <v>-0.3538545853123858</v>
       </c>
       <c r="X3">
-        <v>0.1041533624241665</v>
+        <v>0.08742480683182866</v>
       </c>
       <c r="Y3">
-        <v>-0.1836691759226993</v>
-      </c>
-      <c r="Z3">
-        <v>17.72714125020087</v>
-      </c>
-      <c r="AA3">
-        <v>-0.6712196689699502</v>
+        <v>-0.4412793921442145</v>
       </c>
       <c r="AB3">
-        <v>0.1041533624241665</v>
-      </c>
-      <c r="AC3">
-        <v>-0.7753730313941167</v>
+        <v>0.08499991742710145</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1898.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1898.8</v>
       </c>
       <c r="AG3">
-        <v>-2795.6</v>
+        <v>-872.2</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.04923329029180085</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.4561352935524166</v>
       </c>
       <c r="AJ3">
-        <v>-0.2245101188564086</v>
+        <v>-0.02436557866154138</v>
       </c>
       <c r="AK3">
-        <v>4.613201320132013</v>
+        <v>-0.6266704986348614</v>
       </c>
       <c r="AL3">
-        <v>51</v>
+        <v>59.3</v>
       </c>
       <c r="AM3">
-        <v>23.5</v>
+        <v>-59.2</v>
       </c>
       <c r="AN3">
-        <v>-0</v>
+        <v>-4.956408248499086</v>
       </c>
       <c r="AO3">
-        <v>-8.190196078431372</v>
+        <v>-7.229342327150085</v>
       </c>
       <c r="AP3">
-        <v>7.199587947463301</v>
+        <v>2.276690159227356</v>
       </c>
       <c r="AQ3">
-        <v>-17.77446808510638</v>
+        <v>7.241554054054054</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/luxembourg/luxembourg_entertainment.xlsx
+++ b/research/traditional_assets/database/data/luxembourg/luxembourg_entertainment.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08985827989162551</v>
+        <v>0.08966795034157579</v>
       </c>
       <c r="C2">
-        <v>91797.10952602555</v>
+        <v>91247.96667478951</v>
       </c>
       <c r="D2">
-        <v>86568.50952602555</v>
+        <v>86944.1036747895</v>
       </c>
       <c r="E2">
-        <v>-2067.8</v>
+        <v>-1143.063</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>924.737</v>
       </c>
       <c r="G2">
         <v>5228.6</v>
@@ -1451,28 +1451,28 @@
         <v>1261.4</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>46.51427109999999</v>
       </c>
       <c r="N2">
-        <v>1261.4</v>
+        <v>1214.8857289</v>
       </c>
       <c r="O2">
-        <v>314.59316</v>
+        <v>302.99250078766</v>
       </c>
       <c r="P2">
-        <v>946.8068400000001</v>
+        <v>911.89322811234</v>
       </c>
       <c r="Q2">
-        <v>969.10684</v>
+        <v>934.19322811234</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08985827989162551</v>
+        <v>0.09019232175916747</v>
       </c>
       <c r="T2">
-        <v>1.017512237681883</v>
+        <v>1.025226830465761</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>27.1185588889084</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08966795034157579</v>
+        <v>0.08947762079152609</v>
       </c>
       <c r="C3">
-        <v>91247.96667478951</v>
+        <v>90702.09720081343</v>
       </c>
       <c r="D3">
-        <v>86944.1036747895</v>
+        <v>87322.97120081342</v>
       </c>
       <c r="E3">
-        <v>-1143.063</v>
+        <v>-218.3260000000002</v>
       </c>
       <c r="F3">
-        <v>924.737</v>
+        <v>1849.474</v>
       </c>
       <c r="G3">
         <v>5228.6</v>
@@ -1533,28 +1533,28 @@
         <v>1261.4</v>
       </c>
       <c r="M3">
-        <v>46.51427109999999</v>
+        <v>93.02854219999999</v>
       </c>
       <c r="N3">
-        <v>1214.8857289</v>
+        <v>1168.3714578</v>
       </c>
       <c r="O3">
-        <v>302.99250078766</v>
+        <v>291.39184157532</v>
       </c>
       <c r="P3">
-        <v>911.89322811234</v>
+        <v>876.9796162246801</v>
       </c>
       <c r="Q3">
-        <v>934.19322811234</v>
+        <v>899.27961622468</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09019232175916747</v>
+        <v>0.09053318080767968</v>
       </c>
       <c r="T3">
-        <v>1.025226830465761</v>
+        <v>1.033098863918699</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>27.1185588889084</v>
+        <v>13.5592794444542</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08947762079152609</v>
+        <v>0.08928729124147637</v>
       </c>
       <c r="C4">
-        <v>90702.09720081343</v>
+        <v>90159.54408357972</v>
       </c>
       <c r="D4">
-        <v>87322.97120081342</v>
+        <v>87705.15508357971</v>
       </c>
       <c r="E4">
-        <v>-218.3260000000002</v>
+        <v>706.4109999999996</v>
       </c>
       <c r="F4">
-        <v>1849.474</v>
+        <v>2774.211</v>
       </c>
       <c r="G4">
         <v>5228.6</v>
@@ -1615,28 +1615,28 @@
         <v>1261.4</v>
       </c>
       <c r="M4">
-        <v>93.02854219999999</v>
+        <v>139.5428133</v>
       </c>
       <c r="N4">
-        <v>1168.3714578</v>
+        <v>1121.8571867</v>
       </c>
       <c r="O4">
-        <v>291.39184157532</v>
+        <v>279.79118236298</v>
       </c>
       <c r="P4">
-        <v>876.9796162246801</v>
+        <v>842.0660043370201</v>
       </c>
       <c r="Q4">
-        <v>899.27961622468</v>
+        <v>864.3660043370201</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09053318080767968</v>
+        <v>0.0908810678778107</v>
       </c>
       <c r="T4">
-        <v>1.033098863918699</v>
+        <v>1.041133207339739</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>13.5592794444542</v>
+        <v>9.039519629636134</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08928729124147637</v>
+        <v>0.08919303849142665</v>
       </c>
       <c r="C5">
-        <v>90159.54408357972</v>
+        <v>89425.30888634695</v>
       </c>
       <c r="D5">
-        <v>87705.15508357971</v>
+        <v>87895.65688634694</v>
       </c>
       <c r="E5">
-        <v>706.4109999999996</v>
+        <v>1631.148</v>
       </c>
       <c r="F5">
-        <v>2774.211</v>
+        <v>3698.948</v>
       </c>
       <c r="G5">
         <v>5228.6</v>
@@ -1697,45 +1697,45 @@
         <v>1261.4</v>
       </c>
       <c r="M5">
-        <v>139.5428133</v>
+        <v>197.893718</v>
       </c>
       <c r="N5">
-        <v>1121.8571867</v>
+        <v>1063.506282</v>
       </c>
       <c r="O5">
-        <v>279.79118236298</v>
+        <v>265.2384667308</v>
       </c>
       <c r="P5">
-        <v>842.0660043370201</v>
+        <v>798.2678152692</v>
       </c>
       <c r="Q5">
-        <v>864.3660043370201</v>
+        <v>820.5678152692</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.0908810678778107</v>
+        <v>0.0912362025952361</v>
       </c>
       <c r="T5">
-        <v>1.041133207339739</v>
+        <v>1.049334932915383</v>
       </c>
       <c r="U5">
-        <v>0.0503</v>
+        <v>0.0535</v>
       </c>
       <c r="V5">
         <v>0.2494</v>
       </c>
       <c r="W5">
-        <v>0.03775517999999999</v>
+        <v>0.04015709999999999</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y5">
-        <v>9.039519629636134</v>
+        <v>6.374128561271461</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08919303849142665</v>
+        <v>0.08905675214137695</v>
       </c>
       <c r="C6">
-        <v>89425.30888634695</v>
+        <v>88777.49924841772</v>
       </c>
       <c r="D6">
-        <v>87895.65688634694</v>
+        <v>88172.58424841771</v>
       </c>
       <c r="E6">
-        <v>1631.148</v>
+        <v>2555.885</v>
       </c>
       <c r="F6">
-        <v>3698.948</v>
+        <v>4623.685</v>
       </c>
       <c r="G6">
         <v>5228.6</v>
@@ -1779,45 +1779,45 @@
         <v>1261.4</v>
       </c>
       <c r="M6">
-        <v>197.893718</v>
+        <v>251.0660955</v>
       </c>
       <c r="N6">
-        <v>1063.506282</v>
+        <v>1010.3339045</v>
       </c>
       <c r="O6">
-        <v>265.2384667308</v>
+        <v>251.9772757823</v>
       </c>
       <c r="P6">
-        <v>798.2678152692</v>
+        <v>758.3566287177</v>
       </c>
       <c r="Q6">
-        <v>820.5678152692</v>
+        <v>780.6566287177</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.0912362025952361</v>
+        <v>0.09159881383302837</v>
       </c>
       <c r="T6">
-        <v>1.049334932915383</v>
+        <v>1.057709326397884</v>
       </c>
       <c r="U6">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V6">
         <v>0.2494</v>
       </c>
       <c r="W6">
-        <v>0.04015709999999999</v>
+        <v>0.04075757999999999</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y6">
-        <v>6.374128561271461</v>
+        <v>5.024174998571243</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08905675214137695</v>
+        <v>0.08894148259132723</v>
       </c>
       <c r="C7">
-        <v>88777.49924841772</v>
+        <v>88088.35021393375</v>
       </c>
       <c r="D7">
-        <v>88172.58424841771</v>
+        <v>88408.17221393375</v>
       </c>
       <c r="E7">
-        <v>2555.885</v>
+        <v>3480.622</v>
       </c>
       <c r="F7">
-        <v>4623.685</v>
+        <v>5548.422</v>
       </c>
       <c r="G7">
         <v>5228.6</v>
@@ -1861,45 +1861,45 @@
         <v>1261.4</v>
       </c>
       <c r="M7">
-        <v>251.0660955</v>
+        <v>306.8277366</v>
       </c>
       <c r="N7">
-        <v>1010.3339045</v>
+        <v>954.5722634000001</v>
       </c>
       <c r="O7">
-        <v>251.9772757823</v>
+        <v>238.07032249196</v>
       </c>
       <c r="P7">
-        <v>758.3566287177</v>
+        <v>716.5019409080401</v>
       </c>
       <c r="Q7">
-        <v>780.6566287177</v>
+        <v>738.80194090804</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09159881383302837</v>
+        <v>0.09196914020353961</v>
       </c>
       <c r="T7">
-        <v>1.057709326397884</v>
+        <v>1.066261898465118</v>
       </c>
       <c r="U7">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V7">
         <v>0.2494</v>
       </c>
       <c r="W7">
-        <v>0.04075757999999999</v>
+        <v>0.04150818</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y7">
-        <v>5.024174998571243</v>
+        <v>4.111101603713358</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08894148259132723</v>
+        <v>0.08878868304127752</v>
       </c>
       <c r="C8">
-        <v>88088.35021393375</v>
+        <v>87477.85240386278</v>
       </c>
       <c r="D8">
-        <v>88408.17221393375</v>
+        <v>88722.41140386277</v>
       </c>
       <c r="E8">
-        <v>3480.621999999999</v>
+        <v>4405.358999999999</v>
       </c>
       <c r="F8">
-        <v>5548.422</v>
+        <v>6473.158999999999</v>
       </c>
       <c r="G8">
         <v>5228.6</v>
@@ -1943,28 +1943,28 @@
         <v>1261.4</v>
       </c>
       <c r="M8">
-        <v>306.8277366</v>
+        <v>357.9656926999999</v>
       </c>
       <c r="N8">
-        <v>954.5722634000001</v>
+        <v>903.4343073000002</v>
       </c>
       <c r="O8">
-        <v>238.07032249196</v>
+        <v>225.3165162406201</v>
       </c>
       <c r="P8">
-        <v>716.5019409080401</v>
+        <v>678.1177910593801</v>
       </c>
       <c r="Q8">
-        <v>738.80194090804</v>
+        <v>700.4177910593801</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09196914020353961</v>
+        <v>0.09234743058201883</v>
       </c>
       <c r="T8">
-        <v>1.066261898465118</v>
+        <v>1.074998396813368</v>
       </c>
       <c r="U8">
         <v>0.0553</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>4.11110160371336</v>
+        <v>3.523801374611451</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08878868304127752</v>
+        <v>0.08863588349122781</v>
       </c>
       <c r="C9">
-        <v>87477.85240386278</v>
+        <v>86869.59643417962</v>
       </c>
       <c r="D9">
-        <v>88722.41140386277</v>
+        <v>89038.89243417961</v>
       </c>
       <c r="E9">
-        <v>4405.359</v>
+        <v>5330.096</v>
       </c>
       <c r="F9">
-        <v>6473.159000000001</v>
+        <v>7397.896</v>
       </c>
       <c r="G9">
         <v>5228.6</v>
@@ -2025,28 +2025,28 @@
         <v>1261.4</v>
       </c>
       <c r="M9">
-        <v>357.9656927</v>
+        <v>409.1036488</v>
       </c>
       <c r="N9">
-        <v>903.4343073</v>
+        <v>852.2963512000001</v>
       </c>
       <c r="O9">
-        <v>225.31651624062</v>
+        <v>212.5627099892801</v>
       </c>
       <c r="P9">
-        <v>678.11779105938</v>
+        <v>639.7336412107201</v>
       </c>
       <c r="Q9">
-        <v>700.41779105938</v>
+        <v>662.03364121072</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09234743058201883</v>
+        <v>0.09273394466437805</v>
       </c>
       <c r="T9">
-        <v>1.074998396813368</v>
+        <v>1.083924819038754</v>
       </c>
       <c r="U9">
         <v>0.0553</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>3.52380137461145</v>
+        <v>3.083326202785019</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08863588349122781</v>
+        <v>0.08865196894117811</v>
       </c>
       <c r="C10">
-        <v>86869.59643417962</v>
+        <v>85911.43668411074</v>
       </c>
       <c r="D10">
-        <v>89038.89243417961</v>
+        <v>89005.46968411074</v>
       </c>
       <c r="E10">
-        <v>5330.096</v>
+        <v>6254.833</v>
       </c>
       <c r="F10">
-        <v>7397.896</v>
+        <v>8322.633</v>
       </c>
       <c r="G10">
         <v>5228.6</v>
@@ -2107,45 +2107,45 @@
         <v>1261.4</v>
       </c>
       <c r="M10">
-        <v>409.1036488</v>
+        <v>481.0481874</v>
       </c>
       <c r="N10">
-        <v>852.2963512000001</v>
+        <v>780.3518126000001</v>
       </c>
       <c r="O10">
-        <v>212.5627099892801</v>
+        <v>194.6197420624401</v>
       </c>
       <c r="P10">
-        <v>639.7336412107201</v>
+        <v>585.73207053756</v>
       </c>
       <c r="Q10">
-        <v>662.03364121072</v>
+        <v>608.03207053756</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09273394466437805</v>
+        <v>0.09312895356173417</v>
       </c>
       <c r="T10">
-        <v>1.083924819038754</v>
+        <v>1.093047426367995</v>
       </c>
       <c r="U10">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V10">
         <v>0.2494</v>
       </c>
       <c r="W10">
-        <v>0.04150818</v>
+        <v>0.04338468</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y10">
-        <v>3.083326202785019</v>
+        <v>2.622190526935972</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08865196894117811</v>
+        <v>0.08899081239112837</v>
       </c>
       <c r="C11">
-        <v>85911.43668411074</v>
+        <v>84288.4280207048</v>
       </c>
       <c r="D11">
-        <v>89005.46968411074</v>
+        <v>88307.19802070479</v>
       </c>
       <c r="E11">
-        <v>6254.833</v>
+        <v>7179.569999999999</v>
       </c>
       <c r="F11">
-        <v>8322.633</v>
+        <v>9247.369999999999</v>
       </c>
       <c r="G11">
         <v>5228.6</v>
@@ -2189,45 +2189,45 @@
         <v>1261.4</v>
       </c>
       <c r="M11">
-        <v>481.0481874</v>
+        <v>592.7564169999999</v>
       </c>
       <c r="N11">
-        <v>780.3518126000001</v>
+        <v>668.6435830000001</v>
       </c>
       <c r="O11">
-        <v>194.6197420624401</v>
+        <v>166.7597096002</v>
       </c>
       <c r="P11">
-        <v>585.73207053756</v>
+        <v>501.8838733998001</v>
       </c>
       <c r="Q11">
-        <v>608.03207053756</v>
+        <v>524.1838733998001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09312895356173417</v>
+        <v>0.09353274043458708</v>
       </c>
       <c r="T11">
-        <v>1.093047426367995</v>
+        <v>1.102372758304552</v>
       </c>
       <c r="U11">
-        <v>0.0578</v>
+        <v>0.0641</v>
       </c>
       <c r="V11">
         <v>0.2494</v>
       </c>
       <c r="W11">
-        <v>0.04338468</v>
+        <v>0.04811346</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y11">
-        <v>2.622190526935972</v>
+        <v>2.128024199862859</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08899081239112837</v>
+        <v>0.08987008784107865</v>
       </c>
       <c r="C12">
-        <v>84288.4280207048</v>
+        <v>81601.80773257736</v>
       </c>
       <c r="D12">
-        <v>88307.19802070479</v>
+        <v>86545.31473257736</v>
       </c>
       <c r="E12">
-        <v>7179.570000000001</v>
+        <v>8104.307</v>
       </c>
       <c r="F12">
-        <v>9247.370000000001</v>
+        <v>10172.107</v>
       </c>
       <c r="G12">
         <v>5228.6</v>
@@ -2271,45 +2271,45 @@
         <v>1261.4</v>
       </c>
       <c r="M12">
-        <v>592.7564170000001</v>
+        <v>771.0457106</v>
       </c>
       <c r="N12">
-        <v>668.643583</v>
+        <v>490.3542894000001</v>
       </c>
       <c r="O12">
-        <v>166.7597096002</v>
+        <v>122.29435977636</v>
       </c>
       <c r="P12">
-        <v>501.8838733998</v>
+        <v>368.0599296236401</v>
       </c>
       <c r="Q12">
-        <v>524.1838733997999</v>
+        <v>390.35992962364</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09353274043458708</v>
+        <v>0.0939456011697513</v>
       </c>
       <c r="T12">
-        <v>1.102372758304552</v>
+        <v>1.111907648262155</v>
       </c>
       <c r="U12">
-        <v>0.0641</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V12">
         <v>0.2494</v>
       </c>
       <c r="W12">
-        <v>0.04811346</v>
+        <v>0.05689548</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y12">
-        <v>2.128024199862859</v>
+        <v>1.635960076891452</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08987008784107865</v>
+        <v>0.09115018369102894</v>
       </c>
       <c r="C13">
-        <v>81601.80773257736</v>
+        <v>78234.1633570174</v>
       </c>
       <c r="D13">
-        <v>86545.31473257736</v>
+        <v>84102.40735701739</v>
       </c>
       <c r="E13">
-        <v>8104.307</v>
+        <v>9029.043999999998</v>
       </c>
       <c r="F13">
-        <v>10172.107</v>
+        <v>11096.844</v>
       </c>
       <c r="G13">
         <v>5228.6</v>
@@ -2353,45 +2353,45 @@
         <v>1261.4</v>
       </c>
       <c r="M13">
-        <v>771.0457106</v>
+        <v>998.7159599999999</v>
       </c>
       <c r="N13">
-        <v>490.3542894000001</v>
+        <v>262.6840400000002</v>
       </c>
       <c r="O13">
-        <v>122.29435977636</v>
+        <v>65.51339957600005</v>
       </c>
       <c r="P13">
-        <v>368.0599296236401</v>
+        <v>197.1706404240002</v>
       </c>
       <c r="Q13">
-        <v>390.35992962364</v>
+        <v>219.4706404240001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0939456011697513</v>
+        <v>0.09436784510344198</v>
       </c>
       <c r="T13">
-        <v>1.111907648262155</v>
+        <v>1.121659240264249</v>
       </c>
       <c r="U13">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V13">
         <v>0.2494</v>
       </c>
       <c r="W13">
-        <v>0.05689548</v>
+        <v>0.06755399999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y13">
-        <v>1.635960076891452</v>
+        <v>1.26302177047416</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09115018369102894</v>
+        <v>0.09465651847501129</v>
       </c>
       <c r="C14">
-        <v>78234.1633570174</v>
+        <v>71273.56449994726</v>
       </c>
       <c r="D14">
-        <v>84102.40735701739</v>
+        <v>78066.54549994726</v>
       </c>
       <c r="E14">
-        <v>9029.043999999998</v>
+        <v>9953.780999999999</v>
       </c>
       <c r="F14">
-        <v>11096.844</v>
+        <v>12021.581</v>
       </c>
       <c r="G14">
         <v>5228.6</v>
@@ -2435,45 +2435,45 @@
         <v>1261.4</v>
       </c>
       <c r="M14">
-        <v>998.7159599999999</v>
+        <v>1425.7595066</v>
       </c>
       <c r="N14">
-        <v>262.6840400000002</v>
+        <v>-164.3595066</v>
       </c>
       <c r="O14">
-        <v>65.51339957600005</v>
+        <v>-40.99126094604001</v>
       </c>
       <c r="P14">
-        <v>197.1706404240002</v>
+        <v>-123.36824565396</v>
       </c>
       <c r="Q14">
-        <v>219.4706404240001</v>
+        <v>-101.0682456539601</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09436784510344198</v>
+        <v>0.09498907226921706</v>
       </c>
       <c r="T14">
-        <v>1.121659240264249</v>
+        <v>1.13600628797268</v>
       </c>
       <c r="U14">
-        <v>0.09</v>
+        <v>0.1186</v>
       </c>
       <c r="V14">
-        <v>0.2494</v>
+        <v>0.2206495264760383</v>
       </c>
       <c r="W14">
-        <v>0.06755399999999999</v>
+        <v>0.09243096615994187</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y14">
-        <v>1.26302177047416</v>
+        <v>0.8847214373538023</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09465651847501129</v>
+        <v>0.09538451847501128</v>
       </c>
       <c r="C15">
-        <v>71273.56449994726</v>
+        <v>69202.65432186947</v>
       </c>
       <c r="D15">
-        <v>78066.54549994726</v>
+        <v>76920.37232186946</v>
       </c>
       <c r="E15">
-        <v>9953.780999999999</v>
+        <v>10878.518</v>
       </c>
       <c r="F15">
-        <v>12021.581</v>
+        <v>12946.318</v>
       </c>
       <c r="G15">
         <v>5228.6</v>
@@ -2517,37 +2517,37 @@
         <v>1261.4</v>
       </c>
       <c r="M15">
-        <v>1425.7595066</v>
+        <v>1535.4333148</v>
       </c>
       <c r="N15">
-        <v>-164.3595066</v>
+        <v>-274.0333148000002</v>
       </c>
       <c r="O15">
-        <v>-40.99126094604001</v>
+        <v>-68.34390871112005</v>
       </c>
       <c r="P15">
-        <v>-123.36824565396</v>
+        <v>-205.6894060888802</v>
       </c>
       <c r="Q15">
-        <v>-101.0682456539601</v>
+        <v>-183.3894060888802</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09498907226921706</v>
+        <v>0.09556103822583586</v>
       </c>
       <c r="T15">
-        <v>1.13600628797268</v>
+        <v>1.149215663414223</v>
       </c>
       <c r="U15">
         <v>0.1186</v>
       </c>
       <c r="V15">
-        <v>0.2206495264760383</v>
+        <v>0.2048888460134641</v>
       </c>
       <c r="W15">
-        <v>0.09243096615994187</v>
+        <v>0.09430018286280316</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.8847214373538023</v>
+        <v>0.8215270489713877</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09538451847501128</v>
+        <v>0.108959865550862</v>
       </c>
       <c r="C16">
-        <v>69202.65432186947</v>
+        <v>51744.93799448093</v>
       </c>
       <c r="D16">
-        <v>76920.37232186946</v>
+        <v>60387.39299448093</v>
       </c>
       <c r="E16">
-        <v>10878.518</v>
+        <v>11803.255</v>
       </c>
       <c r="F16">
-        <v>12946.318</v>
+        <v>13871.055</v>
       </c>
       <c r="G16">
         <v>5228.6</v>
@@ -2599,45 +2599,45 @@
         <v>1261.4</v>
       </c>
       <c r="M16">
-        <v>1535.4333148</v>
+        <v>2785.307844</v>
       </c>
       <c r="N16">
-        <v>-274.0333148000002</v>
+        <v>-1523.907844</v>
       </c>
       <c r="O16">
-        <v>-68.34390871112005</v>
+        <v>-380.0626162936001</v>
       </c>
       <c r="P16">
-        <v>-205.6894060888802</v>
+        <v>-1143.8452277064</v>
       </c>
       <c r="Q16">
-        <v>-183.3894060888802</v>
+        <v>-1121.5452277064</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09556103822583586</v>
+        <v>0.09675510582361127</v>
       </c>
       <c r="T16">
-        <v>1.149215663414223</v>
+        <v>1.176792282300491</v>
       </c>
       <c r="U16">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V16">
-        <v>0.2048888460134641</v>
+        <v>0.1129473572114063</v>
       </c>
       <c r="W16">
-        <v>0.09430018286280316</v>
+        <v>0.1781201706719496</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y16">
-        <v>0.8215270489713877</v>
+        <v>0.4528763320425273</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.108959865550862</v>
+        <v>0.110509865550862</v>
       </c>
       <c r="C17">
-        <v>51744.93799448093</v>
+        <v>49373.73748625626</v>
       </c>
       <c r="D17">
-        <v>60387.39299448093</v>
+        <v>58940.92948625626</v>
       </c>
       <c r="E17">
-        <v>11803.255</v>
+        <v>12727.992</v>
       </c>
       <c r="F17">
-        <v>13871.055</v>
+        <v>14795.792</v>
       </c>
       <c r="G17">
         <v>5228.6</v>
@@ -2681,37 +2681,37 @@
         <v>1261.4</v>
       </c>
       <c r="M17">
-        <v>2785.307844</v>
+        <v>2970.9950336</v>
       </c>
       <c r="N17">
-        <v>-1523.907844</v>
+        <v>-1709.5950336</v>
       </c>
       <c r="O17">
-        <v>-380.0626162936</v>
+        <v>-426.37300137984</v>
       </c>
       <c r="P17">
-        <v>-1143.8452277064</v>
+        <v>-1283.22203222016</v>
       </c>
       <c r="Q17">
-        <v>-1121.5452277064</v>
+        <v>-1260.92203222016</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09675510582361127</v>
+        <v>0.09736171422627332</v>
       </c>
       <c r="T17">
-        <v>1.176792282300491</v>
+        <v>1.19080171423264</v>
       </c>
       <c r="U17">
         <v>0.2008</v>
       </c>
       <c r="V17">
-        <v>0.1129473572114063</v>
+        <v>0.1058881473856934</v>
       </c>
       <c r="W17">
-        <v>0.1781201706719496</v>
+        <v>0.1795376600049528</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.4528763320425274</v>
+        <v>0.4245715612898694</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.110509865550862</v>
+        <v>0.112059865550862</v>
       </c>
       <c r="C18">
-        <v>49373.73748625626</v>
+        <v>47070.21047598121</v>
       </c>
       <c r="D18">
-        <v>58940.92948625626</v>
+        <v>57562.13947598122</v>
       </c>
       <c r="E18">
-        <v>12727.992</v>
+        <v>13652.729</v>
       </c>
       <c r="F18">
-        <v>14795.792</v>
+        <v>15720.529</v>
       </c>
       <c r="G18">
         <v>5228.6</v>
@@ -2763,37 +2763,37 @@
         <v>1261.4</v>
       </c>
       <c r="M18">
-        <v>2970.9950336</v>
+        <v>3156.6822232</v>
       </c>
       <c r="N18">
-        <v>-1709.5950336</v>
+        <v>-1895.2822232</v>
       </c>
       <c r="O18">
-        <v>-426.37300137984</v>
+        <v>-472.6833864660801</v>
       </c>
       <c r="P18">
-        <v>-1283.22203222016</v>
+        <v>-1422.59883673392</v>
       </c>
       <c r="Q18">
-        <v>-1260.92203222016</v>
+        <v>-1400.29883673392</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09736171422627332</v>
+        <v>0.09798293969887902</v>
       </c>
       <c r="T18">
-        <v>1.19080171423264</v>
+        <v>1.205148722837853</v>
       </c>
       <c r="U18">
         <v>0.2008</v>
       </c>
       <c r="V18">
-        <v>0.1058881473856934</v>
+        <v>0.09965943283359383</v>
       </c>
       <c r="W18">
-        <v>0.1795376600049528</v>
+        <v>0.1807883858870144</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.4245715612898694</v>
+        <v>0.3995967635669359</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.112059865550862</v>
+        <v>0.113609865550862</v>
       </c>
       <c r="C19">
-        <v>47070.21047598121</v>
+        <v>44829.71631494028</v>
       </c>
       <c r="D19">
-        <v>57562.13947598122</v>
+        <v>56246.38231494028</v>
       </c>
       <c r="E19">
-        <v>13652.729</v>
+        <v>14577.466</v>
       </c>
       <c r="F19">
-        <v>15720.529</v>
+        <v>16645.266</v>
       </c>
       <c r="G19">
         <v>5228.6</v>
@@ -2845,37 +2845,37 @@
         <v>1261.4</v>
       </c>
       <c r="M19">
-        <v>3156.6822232</v>
+        <v>3342.3694128</v>
       </c>
       <c r="N19">
-        <v>-1895.2822232</v>
+        <v>-2080.9694128</v>
       </c>
       <c r="O19">
-        <v>-472.6833864660801</v>
+        <v>-518.99377155232</v>
       </c>
       <c r="P19">
-        <v>-1422.59883673392</v>
+        <v>-1561.97564124768</v>
       </c>
       <c r="Q19">
-        <v>-1400.29883673392</v>
+        <v>-1539.67564124768</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09798293969887902</v>
+        <v>0.09861931701227997</v>
       </c>
       <c r="T19">
-        <v>1.205148722837853</v>
+        <v>1.219845658482217</v>
       </c>
       <c r="U19">
         <v>0.2008</v>
       </c>
       <c r="V19">
-        <v>0.09965943283359383</v>
+        <v>0.09412279767617195</v>
       </c>
       <c r="W19">
-        <v>0.1807883858870144</v>
+        <v>0.1819001422266247</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.3995967635669359</v>
+        <v>0.3773969433687728</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.113609865550862</v>
+        <v>0.115159865550862</v>
       </c>
       <c r="C20">
-        <v>44829.71631494028</v>
+        <v>42648.02917676236</v>
       </c>
       <c r="D20">
-        <v>56246.38231494027</v>
+        <v>54989.43217676236</v>
       </c>
       <c r="E20">
-        <v>14577.466</v>
+        <v>15502.203</v>
       </c>
       <c r="F20">
-        <v>16645.266</v>
+        <v>17570.003</v>
       </c>
       <c r="G20">
         <v>5228.6</v>
@@ -2927,37 +2927,37 @@
         <v>1261.4</v>
       </c>
       <c r="M20">
-        <v>3342.3694128</v>
+        <v>3528.0566024</v>
       </c>
       <c r="N20">
-        <v>-2080.9694128</v>
+        <v>-2266.6566024</v>
       </c>
       <c r="O20">
-        <v>-518.99377155232</v>
+        <v>-565.3041566385601</v>
       </c>
       <c r="P20">
-        <v>-1561.97564124768</v>
+        <v>-1701.35244576144</v>
       </c>
       <c r="Q20">
-        <v>-1539.67564124768</v>
+        <v>-1679.05244576144</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09861931701227997</v>
+        <v>0.09927140734576492</v>
       </c>
       <c r="T20">
-        <v>1.219845658482217</v>
+        <v>1.234905481426442</v>
       </c>
       <c r="U20">
         <v>0.2008</v>
       </c>
       <c r="V20">
-        <v>0.09412279767617195</v>
+        <v>0.08916896621953131</v>
       </c>
       <c r="W20">
-        <v>0.1819001422266247</v>
+        <v>0.1828948715831181</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.3773969433687728</v>
+        <v>0.3575339463493636</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.115159865550862</v>
+        <v>0.116709865550862</v>
       </c>
       <c r="C21">
-        <v>42648.02917676236</v>
+        <v>40521.29271996116</v>
       </c>
       <c r="D21">
-        <v>54989.43217676236</v>
+        <v>53787.43271996116</v>
       </c>
       <c r="E21">
-        <v>15502.203</v>
+        <v>16426.94</v>
       </c>
       <c r="F21">
-        <v>17570.003</v>
+        <v>18494.74</v>
       </c>
       <c r="G21">
         <v>5228.6</v>
@@ -3009,37 +3009,37 @@
         <v>1261.4</v>
       </c>
       <c r="M21">
-        <v>3528.0566024</v>
+        <v>3713.743792</v>
       </c>
       <c r="N21">
-        <v>-2266.6566024</v>
+        <v>-2452.343792</v>
       </c>
       <c r="O21">
-        <v>-565.3041566385601</v>
+        <v>-611.6145417248</v>
       </c>
       <c r="P21">
-        <v>-1701.35244576144</v>
+        <v>-1840.7292502752</v>
       </c>
       <c r="Q21">
-        <v>-1679.05244576144</v>
+        <v>-1818.4292502752</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09927140734576492</v>
+        <v>0.09993979993758698</v>
       </c>
       <c r="T21">
-        <v>1.234905481426442</v>
+        <v>1.250341799944272</v>
       </c>
       <c r="U21">
         <v>0.2008</v>
       </c>
       <c r="V21">
-        <v>0.08916896621953131</v>
+        <v>0.08471051790855474</v>
       </c>
       <c r="W21">
-        <v>0.1828948715831181</v>
+        <v>0.1837901280039622</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.3575339463493636</v>
+        <v>0.3396572490318955</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.116709865550862</v>
+        <v>0.118259865550862</v>
       </c>
       <c r="C22">
-        <v>40521.29271996116</v>
+        <v>38445.98056939838</v>
       </c>
       <c r="D22">
-        <v>53787.43271996116</v>
+        <v>52636.85756939839</v>
       </c>
       <c r="E22">
-        <v>16426.94</v>
+        <v>17351.677</v>
       </c>
       <c r="F22">
-        <v>18494.74</v>
+        <v>19419.477</v>
       </c>
       <c r="G22">
         <v>5228.6</v>
@@ -3091,37 +3091,37 @@
         <v>1261.4</v>
       </c>
       <c r="M22">
-        <v>3713.743792</v>
+        <v>3899.4309816</v>
       </c>
       <c r="N22">
-        <v>-2452.343792</v>
+        <v>-2638.0309816</v>
       </c>
       <c r="O22">
-        <v>-611.6145417248</v>
+        <v>-657.9249268110401</v>
       </c>
       <c r="P22">
-        <v>-1840.7292502752</v>
+        <v>-1980.10605478896</v>
       </c>
       <c r="Q22">
-        <v>-1818.4292502752</v>
+        <v>-1957.80605478896</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09993979993758698</v>
+        <v>0.1006251138608476</v>
       </c>
       <c r="T22">
-        <v>1.250341799944272</v>
+        <v>1.266168911335972</v>
       </c>
       <c r="U22">
         <v>0.2008</v>
       </c>
       <c r="V22">
-        <v>0.08471051790855474</v>
+        <v>0.08067668372243308</v>
       </c>
       <c r="W22">
-        <v>0.1837901280039622</v>
+        <v>0.1846001219085354</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.3396572490318955</v>
+        <v>0.323483094316091</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.118259865550862</v>
+        <v>0.119809865550862</v>
       </c>
       <c r="C23">
-        <v>38445.9805693984</v>
+        <v>36418.86176360389</v>
       </c>
       <c r="D23">
-        <v>52636.8575693984</v>
+        <v>51534.47576360389</v>
       </c>
       <c r="E23">
-        <v>17351.677</v>
+        <v>18276.414</v>
       </c>
       <c r="F23">
-        <v>19419.477</v>
+        <v>20344.214</v>
       </c>
       <c r="G23">
         <v>5228.6</v>
@@ -3173,37 +3173,37 @@
         <v>1261.4</v>
       </c>
       <c r="M23">
-        <v>3899.4309816</v>
+        <v>4085.1181712</v>
       </c>
       <c r="N23">
-        <v>-2638.0309816</v>
+        <v>-2823.7181712</v>
       </c>
       <c r="O23">
-        <v>-657.92492681104</v>
+        <v>-704.2353118972801</v>
       </c>
       <c r="P23">
-        <v>-1980.10605478896</v>
+        <v>-2119.48285930272</v>
       </c>
       <c r="Q23">
-        <v>-1957.80605478896</v>
+        <v>-2097.18285930272</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1006251138608476</v>
+        <v>0.1013279999359867</v>
       </c>
       <c r="T23">
-        <v>1.266168911335972</v>
+        <v>1.282401846096689</v>
       </c>
       <c r="U23">
         <v>0.2008</v>
       </c>
       <c r="V23">
-        <v>0.0806766837224331</v>
+        <v>0.07700956173504978</v>
       </c>
       <c r="W23">
-        <v>0.1846001219085354</v>
+        <v>0.185336480003602</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.323483094316091</v>
+        <v>0.3087793173017233</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.119809865550862</v>
+        <v>0.121359865550862</v>
       </c>
       <c r="C24">
-        <v>36418.86176360389</v>
+        <v>34436.97045488141</v>
       </c>
       <c r="D24">
-        <v>51534.47576360389</v>
+        <v>50477.32145488141</v>
       </c>
       <c r="E24">
-        <v>18276.414</v>
+        <v>19201.151</v>
       </c>
       <c r="F24">
-        <v>20344.214</v>
+        <v>21268.951</v>
       </c>
       <c r="G24">
         <v>5228.6</v>
@@ -3255,37 +3255,37 @@
         <v>1261.4</v>
       </c>
       <c r="M24">
-        <v>4085.1181712</v>
+        <v>4270.8053608</v>
       </c>
       <c r="N24">
-        <v>-2823.7181712</v>
+        <v>-3009.4053608</v>
       </c>
       <c r="O24">
-        <v>-704.2353118972801</v>
+        <v>-750.54569698352</v>
       </c>
       <c r="P24">
-        <v>-2119.48285930272</v>
+        <v>-2258.85966381648</v>
       </c>
       <c r="Q24">
-        <v>-2097.18285930272</v>
+        <v>-2236.55966381648</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1013279999359867</v>
+        <v>0.1020491427922982</v>
       </c>
       <c r="T24">
-        <v>1.282401846096689</v>
+        <v>1.299056415526517</v>
       </c>
       <c r="U24">
         <v>0.2008</v>
       </c>
       <c r="V24">
-        <v>0.07700956173504978</v>
+        <v>0.0736613199204824</v>
       </c>
       <c r="W24">
-        <v>0.185336480003602</v>
+        <v>0.1860088069599671</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.3087793173017233</v>
+        <v>0.2953541295929526</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.121359865550862</v>
+        <v>0.122909865550862</v>
       </c>
       <c r="C25">
-        <v>34436.97045488141</v>
+        <v>32497.57926379791</v>
       </c>
       <c r="D25">
-        <v>50477.32145488141</v>
+        <v>49462.66726379791</v>
       </c>
       <c r="E25">
-        <v>19201.151</v>
+        <v>20125.888</v>
       </c>
       <c r="F25">
-        <v>21268.951</v>
+        <v>22193.688</v>
       </c>
       <c r="G25">
         <v>5228.6</v>
@@ -3337,37 +3337,37 @@
         <v>1261.4</v>
       </c>
       <c r="M25">
-        <v>4270.8053608</v>
+        <v>4456.4925504</v>
       </c>
       <c r="N25">
-        <v>-3009.4053608</v>
+        <v>-3195.0925504</v>
       </c>
       <c r="O25">
-        <v>-750.54569698352</v>
+        <v>-796.8560820697601</v>
       </c>
       <c r="P25">
-        <v>-2258.85966381648</v>
+        <v>-2398.23646833024</v>
       </c>
       <c r="Q25">
-        <v>-2236.55966381648</v>
+        <v>-2375.93646833024</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1020491427922982</v>
+        <v>0.1027892630921968</v>
       </c>
       <c r="T25">
-        <v>1.299056415526517</v>
+        <v>1.316149263099234</v>
       </c>
       <c r="U25">
         <v>0.2008</v>
       </c>
       <c r="V25">
-        <v>0.0736613199204824</v>
+        <v>0.07059209825712895</v>
       </c>
       <c r="W25">
-        <v>0.1860088069599671</v>
+        <v>0.1866251066699685</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.2953541295929526</v>
+        <v>0.2830477075265796</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.122909865550862</v>
+        <v>0.124459865550862</v>
       </c>
       <c r="C26">
-        <v>32497.57926379791</v>
+        <v>30598.17578398665</v>
       </c>
       <c r="D26">
-        <v>49462.66726379791</v>
+        <v>48488.00078398665</v>
       </c>
       <c r="E26">
-        <v>20125.888</v>
+        <v>21050.625</v>
       </c>
       <c r="F26">
-        <v>22193.688</v>
+        <v>23118.425</v>
       </c>
       <c r="G26">
         <v>5228.6</v>
@@ -3419,37 +3419,37 @@
         <v>1261.4</v>
       </c>
       <c r="M26">
-        <v>4456.492550399999</v>
+        <v>4642.17974</v>
       </c>
       <c r="N26">
-        <v>-3195.092550399999</v>
+        <v>-3380.779739999999</v>
       </c>
       <c r="O26">
-        <v>-796.8560820697599</v>
+        <v>-843.166467156</v>
       </c>
       <c r="P26">
-        <v>-2398.236468330239</v>
+        <v>-2537.613272844</v>
       </c>
       <c r="Q26">
-        <v>-2375.936468330239</v>
+        <v>-2515.313272844</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1027892630921968</v>
+        <v>0.1035491199334261</v>
       </c>
       <c r="T26">
-        <v>1.316149263099234</v>
+        <v>1.333697919940557</v>
       </c>
       <c r="U26">
         <v>0.2008</v>
       </c>
       <c r="V26">
-        <v>0.07059209825712896</v>
+        <v>0.06776841432684381</v>
       </c>
       <c r="W26">
-        <v>0.1866251066699685</v>
+        <v>0.1871921024031698</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.2830477075265797</v>
+        <v>0.2717257992255164</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.124459865550862</v>
+        <v>0.126009865550862</v>
       </c>
       <c r="C27">
-        <v>30598.17578398665</v>
+        <v>28736.44181112024</v>
       </c>
       <c r="D27">
-        <v>48488.00078398665</v>
+        <v>47551.00381112024</v>
       </c>
       <c r="E27">
-        <v>21050.625</v>
+        <v>21975.362</v>
       </c>
       <c r="F27">
-        <v>23118.425</v>
+        <v>24043.162</v>
       </c>
       <c r="G27">
         <v>5228.6</v>
@@ -3501,37 +3501,37 @@
         <v>1261.4</v>
       </c>
       <c r="M27">
-        <v>4642.17974</v>
+        <v>4827.8669296</v>
       </c>
       <c r="N27">
-        <v>-3380.779739999999</v>
+        <v>-3566.4669296</v>
       </c>
       <c r="O27">
-        <v>-843.166467156</v>
+        <v>-889.4768522422399</v>
       </c>
       <c r="P27">
-        <v>-2537.613272844</v>
+        <v>-2676.99007735776</v>
       </c>
       <c r="Q27">
-        <v>-2515.313272844</v>
+        <v>-2654.69007735776</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1035491199334261</v>
+        <v>0.10432951344604</v>
       </c>
       <c r="T27">
-        <v>1.333697919940557</v>
+        <v>1.351720864804619</v>
       </c>
       <c r="U27">
         <v>0.2008</v>
       </c>
       <c r="V27">
-        <v>0.06776841432684381</v>
+        <v>0.06516193685273443</v>
       </c>
       <c r="W27">
-        <v>0.1871921024031698</v>
+        <v>0.1877154830799709</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.2717257992255164</v>
+        <v>0.261274806947612</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.126009865550862</v>
+        <v>0.127559865550862</v>
       </c>
       <c r="C28">
-        <v>28736.44181112024</v>
+        <v>26910.23493454142</v>
       </c>
       <c r="D28">
-        <v>47551.00381112024</v>
+        <v>46649.53393454142</v>
       </c>
       <c r="E28">
-        <v>21975.362</v>
+        <v>22900.099</v>
       </c>
       <c r="F28">
-        <v>24043.162</v>
+        <v>24967.899</v>
       </c>
       <c r="G28">
         <v>5228.6</v>
@@ -3583,37 +3583,37 @@
         <v>1261.4</v>
       </c>
       <c r="M28">
-        <v>4827.8669296</v>
+        <v>5013.5541192</v>
       </c>
       <c r="N28">
-        <v>-3566.4669296</v>
+        <v>-3752.1541192</v>
       </c>
       <c r="O28">
-        <v>-889.4768522422399</v>
+        <v>-935.78723732848</v>
       </c>
       <c r="P28">
-        <v>-2676.99007735776</v>
+        <v>-2816.36688187152</v>
       </c>
       <c r="Q28">
-        <v>-2654.69007735776</v>
+        <v>-2794.06688187152</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.10432951344604</v>
+        <v>0.105131287602835</v>
       </c>
       <c r="T28">
-        <v>1.351720864804619</v>
+        <v>1.370237588980024</v>
       </c>
       <c r="U28">
         <v>0.2008</v>
       </c>
       <c r="V28">
-        <v>0.06516193685273443</v>
+        <v>0.06274853178411463</v>
       </c>
       <c r="W28">
-        <v>0.1877154830799709</v>
+        <v>0.1882000948177498</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.261274806947612</v>
+        <v>0.2515979622458485</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.127559865550862</v>
+        <v>0.129109865550862</v>
       </c>
       <c r="C29">
-        <v>26910.23493454142</v>
+        <v>25117.57218384633</v>
       </c>
       <c r="D29">
-        <v>46649.53393454142</v>
+        <v>45781.60818384634</v>
       </c>
       <c r="E29">
-        <v>22900.099</v>
+        <v>23824.836</v>
       </c>
       <c r="F29">
-        <v>24967.899</v>
+        <v>25892.636</v>
       </c>
       <c r="G29">
         <v>5228.6</v>
@@ -3665,37 +3665,37 @@
         <v>1261.4</v>
       </c>
       <c r="M29">
-        <v>5013.5541192</v>
+        <v>5199.2413088</v>
       </c>
       <c r="N29">
-        <v>-3752.1541192</v>
+        <v>-3937.8413088</v>
       </c>
       <c r="O29">
-        <v>-935.78723732848</v>
+        <v>-982.0976224147201</v>
       </c>
       <c r="P29">
-        <v>-2816.36688187152</v>
+        <v>-2955.74368638528</v>
       </c>
       <c r="Q29">
-        <v>-2794.06688187152</v>
+        <v>-2933.44368638528</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.105131287602835</v>
+        <v>0.1059553332639855</v>
       </c>
       <c r="T29">
-        <v>1.370237588980024</v>
+        <v>1.389268666604747</v>
       </c>
       <c r="U29">
         <v>0.2008</v>
       </c>
       <c r="V29">
-        <v>0.06274853178411463</v>
+        <v>0.06050751279182482</v>
       </c>
       <c r="W29">
-        <v>0.1882000948177498</v>
+        <v>0.1886500914314016</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.2515979622458485</v>
+        <v>0.2426123207370683</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.129109865550862</v>
+        <v>0.130659865550862</v>
       </c>
       <c r="C30">
-        <v>25117.57218384633</v>
+        <v>23356.61546767873</v>
       </c>
       <c r="D30">
-        <v>45781.60818384634</v>
+        <v>44945.38846767873</v>
       </c>
       <c r="E30">
-        <v>23824.836</v>
+        <v>24749.573</v>
       </c>
       <c r="F30">
-        <v>25892.636</v>
+        <v>26817.373</v>
       </c>
       <c r="G30">
         <v>5228.6</v>
@@ -3747,37 +3747,37 @@
         <v>1261.4</v>
       </c>
       <c r="M30">
-        <v>5199.2413088</v>
+        <v>5384.928498400001</v>
       </c>
       <c r="N30">
-        <v>-3937.8413088</v>
+        <v>-4123.528498400001</v>
       </c>
       <c r="O30">
-        <v>-982.0976224147201</v>
+        <v>-1028.40800750096</v>
       </c>
       <c r="P30">
-        <v>-2955.74368638528</v>
+        <v>-3095.12049089904</v>
       </c>
       <c r="Q30">
-        <v>-2933.44368638528</v>
+        <v>-3072.82049089904</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1059553332639855</v>
+        <v>0.1068025914789713</v>
       </c>
       <c r="T30">
-        <v>1.389268666604747</v>
+        <v>1.408835830923123</v>
       </c>
       <c r="U30">
         <v>0.2008</v>
       </c>
       <c r="V30">
-        <v>0.06050751279182482</v>
+        <v>0.05842104683348603</v>
       </c>
       <c r="W30">
-        <v>0.1886500914314016</v>
+        <v>0.189069053795836</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.2426123207370683</v>
+        <v>0.2342463786426865</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.130659865550862</v>
+        <v>0.132209865550862</v>
       </c>
       <c r="C31">
-        <v>23356.61546767874</v>
+        <v>21625.65857969736</v>
       </c>
       <c r="D31">
-        <v>44945.38846767874</v>
+        <v>44139.16857969736</v>
       </c>
       <c r="E31">
-        <v>24749.573</v>
+        <v>25674.31</v>
       </c>
       <c r="F31">
-        <v>26817.373</v>
+        <v>27742.11</v>
       </c>
       <c r="G31">
         <v>5228.6</v>
@@ -3829,37 +3829,37 @@
         <v>1261.4</v>
       </c>
       <c r="M31">
-        <v>5384.9284984</v>
+        <v>5570.615688</v>
       </c>
       <c r="N31">
-        <v>-4123.528498399999</v>
+        <v>-4309.215688</v>
       </c>
       <c r="O31">
-        <v>-1028.40800750096</v>
+        <v>-1074.7183925872</v>
       </c>
       <c r="P31">
-        <v>-3095.120490899039</v>
+        <v>-3234.4972954128</v>
       </c>
       <c r="Q31">
-        <v>-3072.820490899039</v>
+        <v>-3212.1972954128</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1068025914789712</v>
+        <v>0.107674057071528</v>
       </c>
       <c r="T31">
-        <v>1.408835830923123</v>
+        <v>1.428962057079168</v>
       </c>
       <c r="U31">
         <v>0.2008</v>
       </c>
       <c r="V31">
-        <v>0.05842104683348604</v>
+        <v>0.05647367860570317</v>
       </c>
       <c r="W31">
-        <v>0.189069053795836</v>
+        <v>0.1894600853359748</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.2342463786426867</v>
+        <v>0.2264381660212637</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.132209865550862</v>
+        <v>0.133759865550862</v>
       </c>
       <c r="C32">
-        <v>21625.65857969736</v>
+        <v>19923.11557840273</v>
       </c>
       <c r="D32">
-        <v>44139.16857969736</v>
+        <v>43361.36257840272</v>
       </c>
       <c r="E32">
-        <v>25674.31</v>
+        <v>26599.047</v>
       </c>
       <c r="F32">
-        <v>27742.11</v>
+        <v>28666.847</v>
       </c>
       <c r="G32">
         <v>5228.6</v>
@@ -3911,37 +3911,37 @@
         <v>1261.4</v>
       </c>
       <c r="M32">
-        <v>5570.615688</v>
+        <v>5756.3028776</v>
       </c>
       <c r="N32">
-        <v>-4309.215688</v>
+        <v>-4494.9028776</v>
       </c>
       <c r="O32">
-        <v>-1074.7183925872</v>
+        <v>-1121.02877767344</v>
       </c>
       <c r="P32">
-        <v>-3234.4972954128</v>
+        <v>-3373.87409992656</v>
       </c>
       <c r="Q32">
-        <v>-3212.1972954128</v>
+        <v>-3351.57409992656</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.107674057071528</v>
+        <v>0.1085707825363327</v>
       </c>
       <c r="T32">
-        <v>1.428962057079168</v>
+        <v>1.449671652109301</v>
       </c>
       <c r="U32">
         <v>0.2008</v>
       </c>
       <c r="V32">
-        <v>0.05647367860570317</v>
+        <v>0.05465194703777726</v>
       </c>
       <c r="W32">
-        <v>0.1894600853359748</v>
+        <v>0.1898258890348143</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.2264381660212637</v>
+        <v>0.2191337090528359</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.133759865550862</v>
+        <v>0.135309865550862</v>
       </c>
       <c r="C33">
-        <v>19923.11557840273</v>
+        <v>18247.51037429025</v>
       </c>
       <c r="D33">
-        <v>43361.36257840272</v>
+        <v>42610.49437429025</v>
       </c>
       <c r="E33">
-        <v>26599.047</v>
+        <v>27523.784</v>
       </c>
       <c r="F33">
-        <v>28666.847</v>
+        <v>29591.584</v>
       </c>
       <c r="G33">
         <v>5228.6</v>
@@ -3993,37 +3993,37 @@
         <v>1261.4</v>
       </c>
       <c r="M33">
-        <v>5756.3028776</v>
+        <v>5941.9900672</v>
       </c>
       <c r="N33">
-        <v>-4494.9028776</v>
+        <v>-4680.590067200001</v>
       </c>
       <c r="O33">
-        <v>-1121.02877767344</v>
+        <v>-1167.33916275968</v>
       </c>
       <c r="P33">
-        <v>-3373.87409992656</v>
+        <v>-3513.25090444032</v>
       </c>
       <c r="Q33">
-        <v>-3351.57409992656</v>
+        <v>-3490.95090444032</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1085707825363327</v>
+        <v>0.1094938822795141</v>
       </c>
       <c r="T33">
-        <v>1.449671652109301</v>
+        <v>1.470990352875614</v>
       </c>
       <c r="U33">
         <v>0.2008</v>
       </c>
       <c r="V33">
-        <v>0.05465194703777726</v>
+        <v>0.05294407369284672</v>
       </c>
       <c r="W33">
-        <v>0.1898258890348143</v>
+        <v>0.1901688300024764</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.2191337090528359</v>
+        <v>0.2122857806449346</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.135309865550862</v>
+        <v>0.136859865550862</v>
       </c>
       <c r="C34">
-        <v>18247.51037429025</v>
+        <v>16597.4673804739</v>
       </c>
       <c r="D34">
-        <v>42610.49437429025</v>
+        <v>41885.1883804739</v>
       </c>
       <c r="E34">
-        <v>27523.784</v>
+        <v>28448.521</v>
       </c>
       <c r="F34">
-        <v>29591.584</v>
+        <v>30516.321</v>
       </c>
       <c r="G34">
         <v>5228.6</v>
@@ -4075,37 +4075,37 @@
         <v>1261.4</v>
       </c>
       <c r="M34">
-        <v>5941.9900672</v>
+        <v>6127.677256800001</v>
       </c>
       <c r="N34">
-        <v>-4680.590067200001</v>
+        <v>-4866.2772568</v>
       </c>
       <c r="O34">
-        <v>-1167.33916275968</v>
+        <v>-1213.64954784592</v>
       </c>
       <c r="P34">
-        <v>-3513.25090444032</v>
+        <v>-3652.62770895408</v>
       </c>
       <c r="Q34">
-        <v>-3490.95090444032</v>
+        <v>-3630.32770895408</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1094938822795141</v>
+        <v>0.1104445372389098</v>
       </c>
       <c r="T34">
-        <v>1.470990352875614</v>
+        <v>1.49294543276928</v>
       </c>
       <c r="U34">
         <v>0.2008</v>
       </c>
       <c r="V34">
-        <v>0.05294407369284672</v>
+        <v>0.05133970782336651</v>
       </c>
       <c r="W34">
-        <v>0.1901688300024764</v>
+        <v>0.190490986669068</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.2122857806449346</v>
+        <v>0.2058528782011488</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.136859865550862</v>
+        <v>0.1504206602834933</v>
       </c>
       <c r="C35">
-        <v>16597.4673804739</v>
+        <v>10243.62641165851</v>
       </c>
       <c r="D35">
-        <v>41885.1883804739</v>
+        <v>36456.08441165851</v>
       </c>
       <c r="E35">
-        <v>28448.521</v>
+        <v>29373.258</v>
       </c>
       <c r="F35">
-        <v>30516.321</v>
+        <v>31441.058</v>
       </c>
       <c r="G35">
         <v>5228.6</v>
@@ -4157,45 +4157,45 @@
         <v>1261.4</v>
       </c>
       <c r="M35">
-        <v>6127.677256800001</v>
+        <v>7413.801476400001</v>
       </c>
       <c r="N35">
-        <v>-4866.2772568</v>
+        <v>-6152.4014764</v>
       </c>
       <c r="O35">
-        <v>-1213.64954784592</v>
+        <v>-1534.40892821416</v>
       </c>
       <c r="P35">
-        <v>-3652.62770895408</v>
+        <v>-4617.99254818584</v>
       </c>
       <c r="Q35">
-        <v>-3630.32770895408</v>
+        <v>-4595.69254818584</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1104445372389098</v>
+        <v>0.111591870731365</v>
       </c>
       <c r="T35">
-        <v>1.49294543276928</v>
+        <v>1.519442742063856</v>
       </c>
       <c r="U35">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.05133970782336651</v>
+        <v>0.04243344807672951</v>
       </c>
       <c r="W35">
-        <v>0.190490986669068</v>
+        <v>0.2257941929435072</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y35">
-        <v>0.2058528782011488</v>
+        <v>0.1701421334271432</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1504206602834933</v>
+        <v>0.1523206602834933</v>
       </c>
       <c r="C36">
-        <v>10243.62641165851</v>
+        <v>8668.625320187373</v>
       </c>
       <c r="D36">
-        <v>36456.08441165851</v>
+        <v>35805.82032018738</v>
       </c>
       <c r="E36">
-        <v>29373.258</v>
+        <v>30297.995</v>
       </c>
       <c r="F36">
-        <v>31441.058</v>
+        <v>32365.795</v>
       </c>
       <c r="G36">
         <v>5228.6</v>
@@ -4239,37 +4239,37 @@
         <v>1261.4</v>
       </c>
       <c r="M36">
-        <v>7413.801476400001</v>
+        <v>7631.854461000001</v>
       </c>
       <c r="N36">
-        <v>-6152.4014764</v>
+        <v>-6370.454461000001</v>
       </c>
       <c r="O36">
-        <v>-1534.40892821416</v>
+        <v>-1588.7913425734</v>
       </c>
       <c r="P36">
-        <v>-4617.99254818584</v>
+        <v>-4781.663118426601</v>
       </c>
       <c r="Q36">
-        <v>-4595.69254818584</v>
+        <v>-4759.363118426601</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.111591870731365</v>
+        <v>0.1126040533580014</v>
       </c>
       <c r="T36">
-        <v>1.519442742063856</v>
+        <v>1.542818784249454</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.04243344807672951</v>
+        <v>0.04122106384596581</v>
       </c>
       <c r="W36">
-        <v>0.2257941929435072</v>
+        <v>0.2260800731451213</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.1701421334271432</v>
+        <v>0.165280929614939</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1523206602834933</v>
+        <v>0.1542206602834933</v>
       </c>
       <c r="C37">
-        <v>8668.625320187373</v>
+        <v>7116.415120610196</v>
       </c>
       <c r="D37">
-        <v>35805.82032018738</v>
+        <v>35178.3471206102</v>
       </c>
       <c r="E37">
-        <v>30297.995</v>
+        <v>31222.732</v>
       </c>
       <c r="F37">
-        <v>32365.795</v>
+        <v>33290.532</v>
       </c>
       <c r="G37">
         <v>5228.6</v>
@@ -4321,37 +4321,37 @@
         <v>1261.4</v>
       </c>
       <c r="M37">
-        <v>7631.854461000001</v>
+        <v>7849.9074456</v>
       </c>
       <c r="N37">
-        <v>-6370.454461000001</v>
+        <v>-6588.5074456</v>
       </c>
       <c r="O37">
-        <v>-1588.7913425734</v>
+        <v>-1643.17375693264</v>
       </c>
       <c r="P37">
-        <v>-4781.663118426601</v>
+        <v>-4945.333688667361</v>
       </c>
       <c r="Q37">
-        <v>-4759.363118426601</v>
+        <v>-4923.03368866736</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1126040533580014</v>
+        <v>0.1136478666917201</v>
       </c>
       <c r="T37">
-        <v>1.542818784249454</v>
+        <v>1.566925327753351</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.04122106384596581</v>
+        <v>0.04007603429468898</v>
       </c>
       <c r="W37">
-        <v>0.2260800731451213</v>
+        <v>0.2263500711133123</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.165280929614939</v>
+        <v>0.1606897926811908</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1542206602834933</v>
+        <v>0.1561206602834933</v>
       </c>
       <c r="C38">
-        <v>7116.415120610189</v>
+        <v>5585.818263015048</v>
       </c>
       <c r="D38">
-        <v>35178.34712061019</v>
+        <v>34572.48726301505</v>
       </c>
       <c r="E38">
-        <v>31222.732</v>
+        <v>32147.469</v>
       </c>
       <c r="F38">
-        <v>33290.532</v>
+        <v>34215.269</v>
       </c>
       <c r="G38">
         <v>5228.6</v>
@@ -4403,37 +4403,37 @@
         <v>1261.4</v>
       </c>
       <c r="M38">
-        <v>7849.9074456</v>
+        <v>8067.960430200001</v>
       </c>
       <c r="N38">
-        <v>-6588.5074456</v>
+        <v>-6806.560430200001</v>
       </c>
       <c r="O38">
-        <v>-1643.17375693264</v>
+        <v>-1697.55617129188</v>
       </c>
       <c r="P38">
-        <v>-4945.333688667361</v>
+        <v>-5109.00425890812</v>
       </c>
       <c r="Q38">
-        <v>-4923.03368866736</v>
+        <v>-5086.70425890812</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1136478666917201</v>
+        <v>0.1147248169566681</v>
       </c>
       <c r="T38">
-        <v>1.566925327753351</v>
+        <v>1.591797158352611</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.04007603429468898</v>
+        <v>0.03899289823267037</v>
       </c>
       <c r="W38">
-        <v>0.2263500711133123</v>
+        <v>0.2266054745967363</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.1606897926811908</v>
+        <v>0.1563468253114288</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1561206602834933</v>
+        <v>0.1580206602834933</v>
       </c>
       <c r="C39">
-        <v>5585.818263015048</v>
+        <v>4075.736945544551</v>
       </c>
       <c r="D39">
-        <v>34572.48726301505</v>
+        <v>33987.14294554455</v>
       </c>
       <c r="E39">
-        <v>32147.469</v>
+        <v>33072.206</v>
       </c>
       <c r="F39">
-        <v>34215.269</v>
+        <v>35140.006</v>
       </c>
       <c r="G39">
         <v>5228.6</v>
@@ -4485,37 +4485,37 @@
         <v>1261.4</v>
       </c>
       <c r="M39">
-        <v>8067.960430200001</v>
+        <v>8286.0134148</v>
       </c>
       <c r="N39">
-        <v>-6806.560430200001</v>
+        <v>-7024.6134148</v>
       </c>
       <c r="O39">
-        <v>-1697.55617129188</v>
+        <v>-1751.93858565112</v>
       </c>
       <c r="P39">
-        <v>-5109.00425890812</v>
+        <v>-5272.67482914888</v>
       </c>
       <c r="Q39">
-        <v>-5086.70425890812</v>
+        <v>-5250.37482914888</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1147248169566681</v>
+        <v>0.1158365075527433</v>
       </c>
       <c r="T39">
-        <v>1.591797158352611</v>
+        <v>1.617471306067976</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.03899289823267037</v>
+        <v>0.03796676933181062</v>
       </c>
       <c r="W39">
-        <v>0.2266054745967363</v>
+        <v>0.2268474357915591</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.1563468253114288</v>
+        <v>0.1522324351716544</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1580206602834933</v>
+        <v>0.1599206602834933</v>
       </c>
       <c r="C40">
-        <v>4075.736945544551</v>
+        <v>2585.146475751091</v>
       </c>
       <c r="D40">
-        <v>33987.14294554455</v>
+        <v>33421.28947575109</v>
       </c>
       <c r="E40">
-        <v>33072.206</v>
+        <v>33996.943</v>
       </c>
       <c r="F40">
-        <v>35140.006</v>
+        <v>36064.743</v>
       </c>
       <c r="G40">
         <v>5228.6</v>
@@ -4567,37 +4567,37 @@
         <v>1261.4</v>
       </c>
       <c r="M40">
-        <v>8286.0134148</v>
+        <v>8504.066399400001</v>
       </c>
       <c r="N40">
-        <v>-7024.6134148</v>
+        <v>-7242.666399400001</v>
       </c>
       <c r="O40">
-        <v>-1751.93858565112</v>
+        <v>-1806.32100001036</v>
       </c>
       <c r="P40">
-        <v>-5272.67482914888</v>
+        <v>-5436.34539938964</v>
       </c>
       <c r="Q40">
-        <v>-5250.37482914888</v>
+        <v>-5414.04539938964</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1158365075527433</v>
+        <v>0.1169846470208211</v>
       </c>
       <c r="T40">
-        <v>1.617471306067976</v>
+        <v>1.64398722911827</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.03796676933181062</v>
+        <v>0.03699326242586676</v>
       </c>
       <c r="W40">
-        <v>0.2268474357915591</v>
+        <v>0.2270769887199806</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.1522324351716544</v>
+        <v>0.1483290393980222</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1599206602834933</v>
+        <v>0.1618206602834933</v>
       </c>
       <c r="C41">
-        <v>2585.146475751091</v>
+        <v>1113.089284254456</v>
       </c>
       <c r="D41">
-        <v>33421.28947575109</v>
+        <v>32873.96928425446</v>
       </c>
       <c r="E41">
-        <v>33996.943</v>
+        <v>34921.68</v>
       </c>
       <c r="F41">
-        <v>36064.743</v>
+        <v>36989.48</v>
       </c>
       <c r="G41">
         <v>5228.6</v>
@@ -4649,37 +4649,37 @@
         <v>1261.4</v>
       </c>
       <c r="M41">
-        <v>8504.066399400001</v>
+        <v>8722.119384000001</v>
       </c>
       <c r="N41">
-        <v>-7242.666399400001</v>
+        <v>-7460.719384000002</v>
       </c>
       <c r="O41">
-        <v>-1806.32100001036</v>
+        <v>-1860.703414369601</v>
       </c>
       <c r="P41">
-        <v>-5436.34539938964</v>
+        <v>-5600.015969630402</v>
       </c>
       <c r="Q41">
-        <v>-5414.04539938964</v>
+        <v>-5577.715969630402</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1169846470208211</v>
+        <v>0.1181710578045015</v>
       </c>
       <c r="T41">
-        <v>1.64398722911827</v>
+        <v>1.671387016270242</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.03699326242586676</v>
+        <v>0.03606843086522008</v>
       </c>
       <c r="W41">
-        <v>0.2270769887199806</v>
+        <v>0.2272950640019811</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.1483290393980222</v>
+        <v>0.1446208134130716</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1618206602834933</v>
+        <v>0.1637206602834933</v>
       </c>
       <c r="C42">
-        <v>1113.089284254456</v>
+        <v>-341.3304828698092</v>
       </c>
       <c r="D42">
-        <v>32873.96928425446</v>
+        <v>32344.28651713019</v>
       </c>
       <c r="E42">
-        <v>34921.68</v>
+        <v>35846.417</v>
       </c>
       <c r="F42">
-        <v>36989.48</v>
+        <v>37914.217</v>
       </c>
       <c r="G42">
         <v>5228.6</v>
@@ -4731,37 +4731,37 @@
         <v>1261.4</v>
       </c>
       <c r="M42">
-        <v>8722.119384000001</v>
+        <v>8940.1723686</v>
       </c>
       <c r="N42">
-        <v>-7460.719384000002</v>
+        <v>-7678.772368600001</v>
       </c>
       <c r="O42">
-        <v>-1860.703414369601</v>
+        <v>-1915.08582872884</v>
       </c>
       <c r="P42">
-        <v>-5600.015969630402</v>
+        <v>-5763.686539871161</v>
       </c>
       <c r="Q42">
-        <v>-5577.715969630402</v>
+        <v>-5741.38653987116</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1181710578045015</v>
+        <v>0.1193976859028828</v>
       </c>
       <c r="T42">
-        <v>1.671387016270242</v>
+        <v>1.699715609766347</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.03606843086522008</v>
+        <v>0.03518871303923912</v>
       </c>
       <c r="W42">
-        <v>0.2272950640019811</v>
+        <v>0.2275025014653474</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.1446208134130716</v>
+        <v>0.1410934765005577</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1637206602834933</v>
+        <v>0.1656206602834933</v>
       </c>
       <c r="C43">
-        <v>-341.3304828698092</v>
+        <v>-1778.951857210173</v>
       </c>
       <c r="D43">
-        <v>32344.28651713019</v>
+        <v>31831.40214278983</v>
       </c>
       <c r="E43">
-        <v>35846.417</v>
+        <v>36771.154</v>
       </c>
       <c r="F43">
-        <v>37914.217</v>
+        <v>38838.95400000001</v>
       </c>
       <c r="G43">
         <v>5228.6</v>
@@ -4813,37 +4813,37 @@
         <v>1261.4</v>
       </c>
       <c r="M43">
-        <v>8940.1723686</v>
+        <v>9158.225353200001</v>
       </c>
       <c r="N43">
-        <v>-7678.772368600001</v>
+        <v>-7896.825353200002</v>
       </c>
       <c r="O43">
-        <v>-1915.08582872884</v>
+        <v>-1969.46824308808</v>
       </c>
       <c r="P43">
-        <v>-5763.686539871161</v>
+        <v>-5927.357110111921</v>
       </c>
       <c r="Q43">
-        <v>-5741.38653987116</v>
+        <v>-5905.057110111921</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1193976859028828</v>
+        <v>0.1206666115218981</v>
       </c>
       <c r="T43">
-        <v>1.699715609766347</v>
+        <v>1.729021051314043</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.03518871303923912</v>
+        <v>0.03435088653830484</v>
       </c>
       <c r="W43">
-        <v>0.2275025014653474</v>
+        <v>0.2277000609542677</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.1410934765005577</v>
+        <v>0.1377341080124492</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1656206602834933</v>
+        <v>0.1675206602834933</v>
       </c>
       <c r="C44">
-        <v>-1778.951857210166</v>
+        <v>-3200.56148286337</v>
       </c>
       <c r="D44">
-        <v>31831.40214278983</v>
+        <v>31334.52951713663</v>
       </c>
       <c r="E44">
-        <v>36771.15399999999</v>
+        <v>37695.891</v>
       </c>
       <c r="F44">
-        <v>38838.954</v>
+        <v>39763.691</v>
       </c>
       <c r="G44">
         <v>5228.6</v>
@@ -4895,37 +4895,37 @@
         <v>1261.4</v>
       </c>
       <c r="M44">
-        <v>9158.2253532</v>
+        <v>9376.2783378</v>
       </c>
       <c r="N44">
-        <v>-7896.8253532</v>
+        <v>-8114.878337800001</v>
       </c>
       <c r="O44">
-        <v>-1969.46824308808</v>
+        <v>-2023.85065744732</v>
       </c>
       <c r="P44">
-        <v>-5927.35711011192</v>
+        <v>-6091.02768035268</v>
       </c>
       <c r="Q44">
-        <v>-5905.057110111919</v>
+        <v>-6068.72768035268</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1206666115218981</v>
+        <v>0.1219800608468436</v>
       </c>
       <c r="T44">
-        <v>1.729021051314043</v>
+        <v>1.759354753968675</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.03435088653830485</v>
+        <v>0.03355202871183264</v>
       </c>
       <c r="W44">
-        <v>0.2277000609542677</v>
+        <v>0.2278884316297499</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.1377341080124492</v>
+        <v>0.134530989221462</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1675206602834933</v>
+        <v>0.1694206602834933</v>
       </c>
       <c r="C45">
-        <v>-3200.56148286337</v>
+        <v>-4606.897642308315</v>
       </c>
       <c r="D45">
-        <v>31334.52951713663</v>
+        <v>30852.93035769168</v>
       </c>
       <c r="E45">
-        <v>37695.891</v>
+        <v>38620.628</v>
       </c>
       <c r="F45">
-        <v>39763.691</v>
+        <v>40688.428</v>
       </c>
       <c r="G45">
         <v>5228.6</v>
@@ -4977,37 +4977,37 @@
         <v>1261.4</v>
       </c>
       <c r="M45">
-        <v>9376.2783378</v>
+        <v>9594.331322400001</v>
       </c>
       <c r="N45">
-        <v>-8114.878337800001</v>
+        <v>-8332.931322400002</v>
       </c>
       <c r="O45">
-        <v>-2023.85065744732</v>
+        <v>-2078.23307180656</v>
       </c>
       <c r="P45">
-        <v>-6091.02768035268</v>
+        <v>-6254.698250593441</v>
       </c>
       <c r="Q45">
-        <v>-6068.72768035268</v>
+        <v>-6232.398250593441</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1219800608468436</v>
+        <v>0.1233404190762516</v>
       </c>
       <c r="T45">
-        <v>1.759354753968675</v>
+        <v>1.790771803146687</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.03355202871183264</v>
+        <v>0.03278948260474553</v>
       </c>
       <c r="W45">
-        <v>0.2278884316297499</v>
+        <v>0.228068240001801</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.134530989221462</v>
+        <v>0.1314734667391561</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1694206602834933</v>
+        <v>0.1713206602834933</v>
       </c>
       <c r="C46">
-        <v>-4606.897642308315</v>
+        <v>-5998.653916643045</v>
       </c>
       <c r="D46">
-        <v>30852.93035769168</v>
+        <v>30385.91108335696</v>
       </c>
       <c r="E46">
-        <v>38620.628</v>
+        <v>39545.365</v>
       </c>
       <c r="F46">
-        <v>40688.428</v>
+        <v>41613.165</v>
       </c>
       <c r="G46">
         <v>5228.6</v>
@@ -5059,37 +5059,37 @@
         <v>1261.4</v>
       </c>
       <c r="M46">
-        <v>9594.331322400001</v>
+        <v>9812.384307</v>
       </c>
       <c r="N46">
-        <v>-8332.931322400002</v>
+        <v>-8550.984307000001</v>
       </c>
       <c r="O46">
-        <v>-2078.23307180656</v>
+        <v>-2132.6154861658</v>
       </c>
       <c r="P46">
-        <v>-6254.698250593441</v>
+        <v>-6418.368820834201</v>
       </c>
       <c r="Q46">
-        <v>-6232.398250593441</v>
+        <v>-6396.068820834201</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1233404190762516</v>
+        <v>0.1247502448776379</v>
       </c>
       <c r="T46">
-        <v>1.790771803146687</v>
+        <v>1.823331290476627</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.03278948260474553</v>
+        <v>0.03206082743575119</v>
       </c>
       <c r="W46">
-        <v>0.228068240001801</v>
+        <v>0.2282400568906499</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.1314734667391561</v>
+        <v>0.1285518341449526</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1713206602834933</v>
+        <v>0.1732206602834933</v>
       </c>
       <c r="C47">
-        <v>-5998.653916643045</v>
+        <v>-7376.482518349796</v>
       </c>
       <c r="D47">
-        <v>30385.91108335696</v>
+        <v>29932.8194816502</v>
       </c>
       <c r="E47">
-        <v>39545.365</v>
+        <v>40470.102</v>
       </c>
       <c r="F47">
-        <v>41613.165</v>
+        <v>42537.902</v>
       </c>
       <c r="G47">
         <v>5228.6</v>
@@ -5141,37 +5141,37 @@
         <v>1261.4</v>
       </c>
       <c r="M47">
-        <v>9812.384307</v>
+        <v>10030.4372916</v>
       </c>
       <c r="N47">
-        <v>-8550.984307000001</v>
+        <v>-8769.037291600001</v>
       </c>
       <c r="O47">
-        <v>-2132.6154861658</v>
+        <v>-2186.997900525041</v>
       </c>
       <c r="P47">
-        <v>-6418.368820834201</v>
+        <v>-6582.039391074961</v>
       </c>
       <c r="Q47">
-        <v>-6396.068820834201</v>
+        <v>-6559.739391074961</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1247502448776379</v>
+        <v>0.1262122864494461</v>
       </c>
       <c r="T47">
-        <v>1.823331290476627</v>
+        <v>1.857096684744713</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.03206082743575119</v>
+        <v>0.03136385292627834</v>
       </c>
       <c r="W47">
-        <v>0.2282400568906499</v>
+        <v>0.2284044034799836</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.1285518341449526</v>
+        <v>0.1257572290548449</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1732206602834933</v>
+        <v>0.1751206602834934</v>
       </c>
       <c r="C48">
-        <v>-7376.482518349796</v>
+        <v>-8740.997330266793</v>
       </c>
       <c r="D48">
-        <v>29932.8194816502</v>
+        <v>29493.04166973321</v>
       </c>
       <c r="E48">
-        <v>40470.102</v>
+        <v>41394.839</v>
       </c>
       <c r="F48">
-        <v>42537.902</v>
+        <v>43462.639</v>
       </c>
       <c r="G48">
         <v>5228.6</v>
@@ -5223,37 +5223,37 @@
         <v>1261.4</v>
       </c>
       <c r="M48">
-        <v>10030.4372916</v>
+        <v>10248.4902762</v>
       </c>
       <c r="N48">
-        <v>-8769.037291600001</v>
+        <v>-8987.090276200002</v>
       </c>
       <c r="O48">
-        <v>-2186.997900525041</v>
+        <v>-2241.380314884281</v>
       </c>
       <c r="P48">
-        <v>-6582.039391074961</v>
+        <v>-6745.709961315722</v>
       </c>
       <c r="Q48">
-        <v>-6559.739391074961</v>
+        <v>-6723.409961315721</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1262122864494461</v>
+        <v>0.1277294994013224</v>
       </c>
       <c r="T48">
-        <v>1.857096684744713</v>
+        <v>1.892136244834236</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.03136385292627834</v>
+        <v>0.03069653690657028</v>
       </c>
       <c r="W48">
-        <v>0.2284044034799836</v>
+        <v>0.2285617565974307</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.1257572290548449</v>
+        <v>0.1230815433302738</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1751206602834934</v>
+        <v>0.1770206602834933</v>
       </c>
       <c r="C49">
-        <v>-8740.997330266793</v>
+        <v>-10092.77668054478</v>
       </c>
       <c r="D49">
-        <v>29493.04166973321</v>
+        <v>29065.99931945522</v>
       </c>
       <c r="E49">
-        <v>41394.839</v>
+        <v>42319.576</v>
       </c>
       <c r="F49">
-        <v>43462.639</v>
+        <v>44387.376</v>
       </c>
       <c r="G49">
         <v>5228.6</v>
@@ -5305,37 +5305,37 @@
         <v>1261.4</v>
       </c>
       <c r="M49">
-        <v>10248.4902762</v>
+        <v>10466.5432608</v>
       </c>
       <c r="N49">
-        <v>-8987.090276200002</v>
+        <v>-9205.143260800001</v>
       </c>
       <c r="O49">
-        <v>-2241.380314884281</v>
+        <v>-2295.76272924352</v>
       </c>
       <c r="P49">
-        <v>-6745.709961315722</v>
+        <v>-6909.38053155648</v>
       </c>
       <c r="Q49">
-        <v>-6723.409961315721</v>
+        <v>-6887.08053155648</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1277294994013224</v>
+        <v>0.1293050666975017</v>
       </c>
       <c r="T49">
-        <v>1.892136244834236</v>
+        <v>1.928523480311817</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.03069653690657028</v>
+        <v>0.03005702572101674</v>
       </c>
       <c r="W49">
-        <v>0.2285617565974307</v>
+        <v>0.2287125533349842</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.1230815433302738</v>
+        <v>0.120517344510893</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1770206602834933</v>
+        <v>0.1789206602834933</v>
       </c>
       <c r="C50">
-        <v>-10092.77668054478</v>
+        <v>-11432.36587996564</v>
       </c>
       <c r="D50">
-        <v>29065.99931945522</v>
+        <v>28651.14712003436</v>
       </c>
       <c r="E50">
-        <v>42319.57599999999</v>
+        <v>43244.31299999999</v>
       </c>
       <c r="F50">
-        <v>44387.376</v>
+        <v>45312.113</v>
       </c>
       <c r="G50">
         <v>5228.6</v>
@@ -5387,37 +5387,37 @@
         <v>1261.4</v>
       </c>
       <c r="M50">
-        <v>10466.5432608</v>
+        <v>10684.5962454</v>
       </c>
       <c r="N50">
-        <v>-9205.1432608</v>
+        <v>-9423.1962454</v>
       </c>
       <c r="O50">
-        <v>-2295.76272924352</v>
+        <v>-2350.14514360276</v>
       </c>
       <c r="P50">
-        <v>-6909.38053155648</v>
+        <v>-7073.05110179724</v>
       </c>
       <c r="Q50">
-        <v>-6887.080531556479</v>
+        <v>-7050.75110179724</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1293050666975017</v>
+        <v>0.1309424209464723</v>
       </c>
       <c r="T50">
-        <v>1.928523480311817</v>
+        <v>1.966337666200284</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.03005702572101674</v>
+        <v>0.02944361703283273</v>
       </c>
       <c r="W50">
-        <v>0.2287125533349842</v>
+        <v>0.2288571951036581</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.120517344510893</v>
+        <v>0.1180578068678136</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1789206602834933</v>
+        <v>0.1808206602834933</v>
       </c>
       <c r="C51">
-        <v>-11432.36587996564</v>
+        <v>-12760.27954503132</v>
       </c>
       <c r="D51">
-        <v>28651.14712003436</v>
+        <v>28247.97045496868</v>
       </c>
       <c r="E51">
-        <v>43244.31299999999</v>
+        <v>44169.05</v>
       </c>
       <c r="F51">
-        <v>45312.113</v>
+        <v>46236.85</v>
       </c>
       <c r="G51">
         <v>5228.6</v>
@@ -5469,37 +5469,37 @@
         <v>1261.4</v>
       </c>
       <c r="M51">
-        <v>10684.5962454</v>
+        <v>10902.64923</v>
       </c>
       <c r="N51">
-        <v>-9423.1962454</v>
+        <v>-9641.249230000001</v>
       </c>
       <c r="O51">
-        <v>-2350.14514360276</v>
+        <v>-2404.527557962001</v>
       </c>
       <c r="P51">
-        <v>-7073.05110179724</v>
+        <v>-7236.721672038</v>
       </c>
       <c r="Q51">
-        <v>-7050.75110179724</v>
+        <v>-7214.421672038</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1309424209464723</v>
+        <v>0.1326452693654017</v>
       </c>
       <c r="T51">
-        <v>1.966337666200284</v>
+        <v>2.00566441952429</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.02944361703283273</v>
+        <v>0.02885474469217607</v>
       </c>
       <c r="W51">
-        <v>0.2288571951036581</v>
+        <v>0.2289960512015849</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.1180578068678136</v>
+        <v>0.1156966507304573</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1808206602834933</v>
+        <v>0.1827206602834933</v>
       </c>
       <c r="C52">
-        <v>-12760.27954503132</v>
+        <v>-14077.00372763265</v>
       </c>
       <c r="D52">
-        <v>28247.97045496868</v>
+        <v>27855.98327236734</v>
       </c>
       <c r="E52">
-        <v>44169.05</v>
+        <v>45093.787</v>
       </c>
       <c r="F52">
-        <v>46236.85</v>
+        <v>47161.587</v>
       </c>
       <c r="G52">
         <v>5228.6</v>
@@ -5551,37 +5551,37 @@
         <v>1261.4</v>
       </c>
       <c r="M52">
-        <v>10902.64923</v>
+        <v>11120.7022146</v>
       </c>
       <c r="N52">
-        <v>-9641.249230000001</v>
+        <v>-9859.3022146</v>
       </c>
       <c r="O52">
-        <v>-2404.527557962001</v>
+        <v>-2458.90997232124</v>
       </c>
       <c r="P52">
-        <v>-7236.721672038</v>
+        <v>-7400.39224227876</v>
       </c>
       <c r="Q52">
-        <v>-7214.421672038</v>
+        <v>-7378.09224227876</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1326452693654017</v>
+        <v>0.1344176218014304</v>
       </c>
       <c r="T52">
-        <v>2.00566441952429</v>
+        <v>2.046596346453357</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.02885474469217607</v>
+        <v>0.02828896538448634</v>
       </c>
       <c r="W52">
-        <v>0.2289960512015849</v>
+        <v>0.2291294619623381</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.1156966507304573</v>
+        <v>0.1134280889514288</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1827206602834933</v>
+        <v>0.1846206602834933</v>
       </c>
       <c r="C53">
-        <v>-14077.00372763265</v>
+        <v>-15382.99786982902</v>
       </c>
       <c r="D53">
-        <v>27855.98327236734</v>
+        <v>27474.72613017098</v>
       </c>
       <c r="E53">
-        <v>45093.787</v>
+        <v>46018.524</v>
       </c>
       <c r="F53">
-        <v>47161.587</v>
+        <v>48086.324</v>
       </c>
       <c r="G53">
         <v>5228.6</v>
@@ -5633,37 +5633,37 @@
         <v>1261.4</v>
       </c>
       <c r="M53">
-        <v>11120.7022146</v>
+        <v>11338.7551992</v>
       </c>
       <c r="N53">
-        <v>-9859.3022146</v>
+        <v>-10077.3551992</v>
       </c>
       <c r="O53">
-        <v>-2458.90997232124</v>
+        <v>-2513.29238668048</v>
       </c>
       <c r="P53">
-        <v>-7400.39224227876</v>
+        <v>-7564.062812519521</v>
       </c>
       <c r="Q53">
-        <v>-7378.09224227876</v>
+        <v>-7541.762812519521</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1344176218014304</v>
+        <v>0.1362638222556268</v>
       </c>
       <c r="T53">
-        <v>2.046596346453357</v>
+        <v>2.089233770337802</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.02828896538448634</v>
+        <v>0.02774494681940007</v>
       </c>
       <c r="W53">
-        <v>0.2291294619623381</v>
+        <v>0.2292577415399855</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.1134280889514288</v>
+        <v>0.1112467795485167</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1846206602834933</v>
+        <v>0.1865206602834933</v>
       </c>
       <c r="C54">
-        <v>-15382.99786982902</v>
+        <v>-16678.69660026833</v>
       </c>
       <c r="D54">
-        <v>27474.72613017098</v>
+        <v>27103.76439973168</v>
       </c>
       <c r="E54">
-        <v>46018.524</v>
+        <v>46943.261</v>
       </c>
       <c r="F54">
-        <v>48086.324</v>
+        <v>49011.061</v>
       </c>
       <c r="G54">
         <v>5228.6</v>
@@ -5715,37 +5715,37 @@
         <v>1261.4</v>
       </c>
       <c r="M54">
-        <v>11338.7551992</v>
+        <v>11556.8081838</v>
       </c>
       <c r="N54">
-        <v>-10077.3551992</v>
+        <v>-10295.4081838</v>
       </c>
       <c r="O54">
-        <v>-2513.29238668048</v>
+        <v>-2567.67480103972</v>
       </c>
       <c r="P54">
-        <v>-7564.062812519521</v>
+        <v>-7727.733382760282</v>
       </c>
       <c r="Q54">
-        <v>-7541.762812519521</v>
+        <v>-7705.433382760281</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1362638222556268</v>
+        <v>0.1381885844312785</v>
       </c>
       <c r="T54">
-        <v>2.089233770337802</v>
+        <v>2.133685552685415</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.02774494681940007</v>
+        <v>0.02722145725676988</v>
       </c>
       <c r="W54">
-        <v>0.2292577415399855</v>
+        <v>0.2293811803788537</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.1112467795485167</v>
+        <v>0.1091477837079786</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1865206602834933</v>
+        <v>0.1884206602834933</v>
       </c>
       <c r="C55">
-        <v>-16678.69660026833</v>
+        <v>-17964.51138701483</v>
       </c>
       <c r="D55">
-        <v>27103.76439973168</v>
+        <v>26742.68661298517</v>
       </c>
       <c r="E55">
-        <v>46943.261</v>
+        <v>47867.998</v>
       </c>
       <c r="F55">
-        <v>49011.061</v>
+        <v>49935.798</v>
       </c>
       <c r="G55">
         <v>5228.6</v>
@@ -5797,37 +5797,37 @@
         <v>1261.4</v>
       </c>
       <c r="M55">
-        <v>11556.8081838</v>
+        <v>11774.8611684</v>
       </c>
       <c r="N55">
-        <v>-10295.4081838</v>
+        <v>-10513.4611684</v>
       </c>
       <c r="O55">
-        <v>-2567.67480103972</v>
+        <v>-2622.057215398961</v>
       </c>
       <c r="P55">
-        <v>-7727.733382760282</v>
+        <v>-7891.40395300104</v>
       </c>
       <c r="Q55">
-        <v>-7705.433382760281</v>
+        <v>-7869.10395300104</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1381885844312785</v>
+        <v>0.1401970319189149</v>
       </c>
       <c r="T55">
-        <v>2.133685552685415</v>
+        <v>2.180070021222055</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.02722145725676988</v>
+        <v>0.02671735619645932</v>
       </c>
       <c r="W55">
-        <v>0.2293811803788537</v>
+        <v>0.2295000474088749</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.1091477837079786</v>
+        <v>0.1071265284541272</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1884206602834933</v>
+        <v>0.1903206602834933</v>
       </c>
       <c r="C56">
-        <v>-17964.51138701483</v>
+        <v>-19240.83205999972</v>
       </c>
       <c r="D56">
-        <v>26742.68661298517</v>
+        <v>26391.10294000028</v>
       </c>
       <c r="E56">
-        <v>47867.998</v>
+        <v>48792.735</v>
       </c>
       <c r="F56">
-        <v>49935.798</v>
+        <v>50860.535</v>
       </c>
       <c r="G56">
         <v>5228.6</v>
@@ -5879,37 +5879,37 @@
         <v>1261.4</v>
       </c>
       <c r="M56">
-        <v>11774.8611684</v>
+        <v>11992.914153</v>
       </c>
       <c r="N56">
-        <v>-10513.4611684</v>
+        <v>-10731.514153</v>
       </c>
       <c r="O56">
-        <v>-2622.057215398961</v>
+        <v>-2676.439629758201</v>
       </c>
       <c r="P56">
-        <v>-7891.40395300104</v>
+        <v>-8055.074523241801</v>
       </c>
       <c r="Q56">
-        <v>-7869.10395300104</v>
+        <v>-8032.774523241801</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1401970319189149</v>
+        <v>0.1422947437393353</v>
       </c>
       <c r="T56">
-        <v>2.180070021222055</v>
+        <v>2.228516021693656</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.02671735619645932</v>
+        <v>0.02623158608379643</v>
       </c>
       <c r="W56">
-        <v>0.2295000474088749</v>
+        <v>0.2296145920014408</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1071265284541272</v>
+        <v>0.1051787733913249</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1903206602834933</v>
+        <v>0.1922206602834933</v>
       </c>
       <c r="C57">
-        <v>-19240.83205999972</v>
+        <v>-20508.02821493671</v>
       </c>
       <c r="D57">
-        <v>26391.10294000028</v>
+        <v>26048.64378506329</v>
       </c>
       <c r="E57">
-        <v>48792.735</v>
+        <v>49717.472</v>
       </c>
       <c r="F57">
-        <v>50860.535</v>
+        <v>51785.272</v>
       </c>
       <c r="G57">
         <v>5228.6</v>
@@ -5961,37 +5961,37 @@
         <v>1261.4</v>
       </c>
       <c r="M57">
-        <v>11992.914153</v>
+        <v>12210.9671376</v>
       </c>
       <c r="N57">
-        <v>-10731.514153</v>
+        <v>-10949.5671376</v>
       </c>
       <c r="O57">
-        <v>-2676.439629758201</v>
+        <v>-2730.822044117441</v>
       </c>
       <c r="P57">
-        <v>-8055.074523241801</v>
+        <v>-8218.745093482561</v>
       </c>
       <c r="Q57">
-        <v>-8032.774523241801</v>
+        <v>-8196.445093482562</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1422947437393353</v>
+        <v>0.1444878060970474</v>
       </c>
       <c r="T57">
-        <v>2.228516021693656</v>
+        <v>2.279164113095784</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.02623158608379643</v>
+        <v>0.02576316490372863</v>
       </c>
       <c r="W57">
-        <v>0.2296145920014408</v>
+        <v>0.2297250457157008</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1051787733913249</v>
+        <v>0.1033005810093369</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1922206602834933</v>
+        <v>0.1941206602834933</v>
       </c>
       <c r="C58">
-        <v>-20508.02821493671</v>
+        <v>-21766.45050933212</v>
       </c>
       <c r="D58">
-        <v>26048.64378506329</v>
+        <v>25714.95849066788</v>
       </c>
       <c r="E58">
-        <v>49717.472</v>
+        <v>50642.209</v>
       </c>
       <c r="F58">
-        <v>51785.272</v>
+        <v>52710.00900000001</v>
       </c>
       <c r="G58">
         <v>5228.6</v>
@@ -6043,37 +6043,37 @@
         <v>1261.4</v>
       </c>
       <c r="M58">
-        <v>12210.9671376</v>
+        <v>12429.0201222</v>
       </c>
       <c r="N58">
-        <v>-10949.5671376</v>
+        <v>-11167.6201222</v>
       </c>
       <c r="O58">
-        <v>-2730.822044117441</v>
+        <v>-2785.20445847668</v>
       </c>
       <c r="P58">
-        <v>-8218.745093482561</v>
+        <v>-8382.415663723321</v>
       </c>
       <c r="Q58">
-        <v>-8196.445093482562</v>
+        <v>-8360.115663723322</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1444878060970474</v>
+        <v>0.1467828713551183</v>
       </c>
       <c r="T58">
-        <v>2.279164113095784</v>
+        <v>2.332167929679407</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.02576316490372863</v>
+        <v>0.02531117955454041</v>
       </c>
       <c r="W58">
-        <v>0.2297250457157008</v>
+        <v>0.2298316238610394</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.1033005810093369</v>
+        <v>0.1014882901144363</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1941206602834933</v>
+        <v>0.1960206602834933</v>
       </c>
       <c r="C59">
-        <v>-21766.45050933212</v>
+        <v>-23016.4318601429</v>
       </c>
       <c r="D59">
-        <v>25714.95849066788</v>
+        <v>25389.71413985711</v>
       </c>
       <c r="E59">
-        <v>50642.209</v>
+        <v>51566.946</v>
       </c>
       <c r="F59">
-        <v>52710.00900000001</v>
+        <v>53634.74600000001</v>
       </c>
       <c r="G59">
         <v>5228.6</v>
@@ -6125,37 +6125,37 @@
         <v>1261.4</v>
       </c>
       <c r="M59">
-        <v>12429.0201222</v>
+        <v>12647.0731068</v>
       </c>
       <c r="N59">
-        <v>-11167.6201222</v>
+        <v>-11385.6731068</v>
       </c>
       <c r="O59">
-        <v>-2785.20445847668</v>
+        <v>-2839.586872835921</v>
       </c>
       <c r="P59">
-        <v>-8382.415663723321</v>
+        <v>-8546.086233964081</v>
       </c>
       <c r="Q59">
-        <v>-8360.115663723322</v>
+        <v>-8523.786233964081</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1467828713551183</v>
+        <v>0.1491872254350021</v>
       </c>
       <c r="T59">
-        <v>2.332167929679407</v>
+        <v>2.387695737528917</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.02531117955454041</v>
+        <v>0.02487477990704834</v>
       </c>
       <c r="W59">
-        <v>0.2298316238610394</v>
+        <v>0.229934526897918</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1014882901144363</v>
+        <v>0.09973849200901497</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1960206602834933</v>
+        <v>0.1979206602834933</v>
       </c>
       <c r="C60">
-        <v>-23016.43186014288</v>
+        <v>-24258.28855168133</v>
       </c>
       <c r="D60">
-        <v>25389.71413985711</v>
+        <v>25072.59444831866</v>
       </c>
       <c r="E60">
-        <v>51566.94599999999</v>
+        <v>52491.68299999999</v>
       </c>
       <c r="F60">
-        <v>53634.74599999999</v>
+        <v>54559.48299999999</v>
       </c>
       <c r="G60">
         <v>5228.6</v>
@@ -6207,37 +6207,37 @@
         <v>1261.4</v>
       </c>
       <c r="M60">
-        <v>12647.0731068</v>
+        <v>12865.1260914</v>
       </c>
       <c r="N60">
-        <v>-11385.6731068</v>
+        <v>-11603.7260914</v>
       </c>
       <c r="O60">
-        <v>-2839.58687283592</v>
+        <v>-2893.96928719516</v>
       </c>
       <c r="P60">
-        <v>-8546.086233964079</v>
+        <v>-8709.756804204841</v>
       </c>
       <c r="Q60">
-        <v>-8523.78623396408</v>
+        <v>-8687.456804204841</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.149187225435002</v>
+        <v>0.1517088650797582</v>
       </c>
       <c r="T60">
-        <v>2.387695737528916</v>
+        <v>2.44593221893206</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.02487477990704834</v>
+        <v>0.02445317346794582</v>
       </c>
       <c r="W60">
-        <v>0.229934526897918</v>
+        <v>0.2300339416962584</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.09973849200901497</v>
+        <v>0.09804800909360789</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1979206602834933</v>
+        <v>0.1998206602834933</v>
       </c>
       <c r="C61">
-        <v>-24258.28855168133</v>
+        <v>-25492.32126151742</v>
       </c>
       <c r="D61">
-        <v>25072.59444831866</v>
+        <v>24763.29873848257</v>
       </c>
       <c r="E61">
-        <v>52491.68299999999</v>
+        <v>53416.41999999999</v>
       </c>
       <c r="F61">
-        <v>54559.48299999999</v>
+        <v>55484.21999999999</v>
       </c>
       <c r="G61">
         <v>5228.6</v>
@@ -6289,37 +6289,37 @@
         <v>1261.4</v>
       </c>
       <c r="M61">
-        <v>12865.1260914</v>
+        <v>13083.179076</v>
       </c>
       <c r="N61">
-        <v>-11603.7260914</v>
+        <v>-11821.779076</v>
       </c>
       <c r="O61">
-        <v>-2893.96928719516</v>
+        <v>-2948.3517015544</v>
       </c>
       <c r="P61">
-        <v>-8709.756804204841</v>
+        <v>-8873.427374445599</v>
       </c>
       <c r="Q61">
-        <v>-8687.456804204841</v>
+        <v>-8851.127374445599</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1517088650797582</v>
+        <v>0.1543565867067522</v>
       </c>
       <c r="T61">
-        <v>2.44593221893206</v>
+        <v>2.507080524405362</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.02445317346794582</v>
+        <v>0.0240456205768134</v>
       </c>
       <c r="W61">
-        <v>0.2300339416962584</v>
+        <v>0.2301300426679874</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.09804800909360789</v>
+        <v>0.09641387560871451</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1998206602834933</v>
+        <v>0.2017206602834933</v>
       </c>
       <c r="C62">
-        <v>-25492.32126151742</v>
+        <v>-26718.81601137284</v>
       </c>
       <c r="D62">
-        <v>24763.29873848257</v>
+        <v>24461.54098862716</v>
       </c>
       <c r="E62">
-        <v>53416.41999999999</v>
+        <v>54341.15699999999</v>
       </c>
       <c r="F62">
-        <v>55484.21999999999</v>
+        <v>56408.95699999999</v>
       </c>
       <c r="G62">
         <v>5228.6</v>
@@ -6371,37 +6371,37 @@
         <v>1261.4</v>
       </c>
       <c r="M62">
-        <v>13083.179076</v>
+        <v>13301.2320606</v>
       </c>
       <c r="N62">
-        <v>-11821.779076</v>
+        <v>-12039.8320606</v>
       </c>
       <c r="O62">
-        <v>-2948.3517015544</v>
+        <v>-3002.73411591364</v>
       </c>
       <c r="P62">
-        <v>-8873.427374445599</v>
+        <v>-9037.09794468636</v>
       </c>
       <c r="Q62">
-        <v>-8851.127374445599</v>
+        <v>-9014.797944686361</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1543565867067522</v>
+        <v>0.1571400889300022</v>
       </c>
       <c r="T62">
-        <v>2.507080524405362</v>
+        <v>2.571364640415756</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.0240456205768134</v>
+        <v>0.02365143007555416</v>
       </c>
       <c r="W62">
-        <v>0.2301300426679874</v>
+        <v>0.2302229927881843</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.09641387560871451</v>
+        <v>0.09483332027086666</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2017206602834933</v>
+        <v>0.2036206602834933</v>
       </c>
       <c r="C63">
-        <v>-26718.81601137284</v>
+        <v>-27938.04504932849</v>
       </c>
       <c r="D63">
-        <v>24461.54098862716</v>
+        <v>24167.04895067151</v>
       </c>
       <c r="E63">
-        <v>54341.15699999999</v>
+        <v>55265.89399999999</v>
       </c>
       <c r="F63">
-        <v>56408.95699999999</v>
+        <v>57333.694</v>
       </c>
       <c r="G63">
         <v>5228.6</v>
@@ -6453,37 +6453,37 @@
         <v>1261.4</v>
       </c>
       <c r="M63">
-        <v>13301.2320606</v>
+        <v>13519.2850452</v>
       </c>
       <c r="N63">
-        <v>-12039.8320606</v>
+        <v>-12257.8850452</v>
       </c>
       <c r="O63">
-        <v>-3002.73411591364</v>
+        <v>-3057.11653027288</v>
       </c>
       <c r="P63">
-        <v>-9037.09794468636</v>
+        <v>-9200.76851492712</v>
       </c>
       <c r="Q63">
-        <v>-9014.797944686361</v>
+        <v>-9178.468514927121</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1571400889300022</v>
+        <v>0.1600700912702654</v>
       </c>
       <c r="T63">
-        <v>2.571364640415756</v>
+        <v>2.639032130953013</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.02365143007555416</v>
+        <v>0.02326995539691619</v>
       </c>
       <c r="W63">
-        <v>0.2302229927881843</v>
+        <v>0.2303129445174072</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.09483332027086666</v>
+        <v>0.09330375058907847</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2036206602834933</v>
+        <v>0.2055206602834933</v>
       </c>
       <c r="C64">
-        <v>-27938.04504932849</v>
+        <v>-29150.2676690647</v>
       </c>
       <c r="D64">
-        <v>24167.04895067151</v>
+        <v>23879.5633309353</v>
       </c>
       <c r="E64">
-        <v>55265.89399999999</v>
+        <v>56190.63099999999</v>
       </c>
       <c r="F64">
-        <v>57333.694</v>
+        <v>58258.431</v>
       </c>
       <c r="G64">
         <v>5228.6</v>
@@ -6535,37 +6535,37 @@
         <v>1261.4</v>
       </c>
       <c r="M64">
-        <v>13519.2850452</v>
+        <v>13737.3380298</v>
       </c>
       <c r="N64">
-        <v>-12257.8850452</v>
+        <v>-12475.9380298</v>
       </c>
       <c r="O64">
-        <v>-3057.11653027288</v>
+        <v>-3111.49894463212</v>
       </c>
       <c r="P64">
-        <v>-9200.76851492712</v>
+        <v>-9364.43908516788</v>
       </c>
       <c r="Q64">
-        <v>-9178.468514927121</v>
+        <v>-9342.139085167881</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1600700912702654</v>
+        <v>0.1631584721154077</v>
       </c>
       <c r="T64">
-        <v>2.639032130953013</v>
+        <v>2.710357323681472</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.02326995539691619</v>
+        <v>0.02290059102553657</v>
       </c>
       <c r="W64">
-        <v>0.2303129445174072</v>
+        <v>0.2304000406361785</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.09330375058907847</v>
+        <v>0.09182273867496615</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2055206602834933</v>
+        <v>0.2074206602834933</v>
       </c>
       <c r="C65">
-        <v>-29150.2676690647</v>
+        <v>-30355.73097131586</v>
       </c>
       <c r="D65">
-        <v>23879.5633309353</v>
+        <v>23598.83702868414</v>
       </c>
       <c r="E65">
-        <v>56190.63099999999</v>
+        <v>57115.36799999999</v>
       </c>
       <c r="F65">
-        <v>58258.431</v>
+        <v>59183.168</v>
       </c>
       <c r="G65">
         <v>5228.6</v>
@@ -6617,37 +6617,37 @@
         <v>1261.4</v>
       </c>
       <c r="M65">
-        <v>13737.3380298</v>
+        <v>13955.3910144</v>
       </c>
       <c r="N65">
-        <v>-12475.9380298</v>
+        <v>-12693.9910144</v>
       </c>
       <c r="O65">
-        <v>-3111.49894463212</v>
+        <v>-3165.88135899136</v>
       </c>
       <c r="P65">
-        <v>-9364.43908516788</v>
+        <v>-9528.10965540864</v>
       </c>
       <c r="Q65">
-        <v>-9342.139085167881</v>
+        <v>-9505.809655408641</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1631584721154077</v>
+        <v>0.1664184296741691</v>
       </c>
       <c r="T65">
-        <v>2.710357323681472</v>
+        <v>2.785645027117069</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.02290059102553657</v>
+        <v>0.02254276929076255</v>
       </c>
       <c r="W65">
-        <v>0.2304000406361785</v>
+        <v>0.2304844150012382</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.09182273867496615</v>
+        <v>0.09038800838316985</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2074206602834933</v>
+        <v>0.2093206602834933</v>
       </c>
       <c r="C66">
-        <v>-30355.73097131586</v>
+        <v>-31554.67057223959</v>
       </c>
       <c r="D66">
-        <v>23598.83702868414</v>
+        <v>23324.6344277604</v>
       </c>
       <c r="E66">
-        <v>57115.36799999999</v>
+        <v>58040.105</v>
       </c>
       <c r="F66">
-        <v>59183.168</v>
+        <v>60107.905</v>
       </c>
       <c r="G66">
         <v>5228.6</v>
@@ -6699,37 +6699,37 @@
         <v>1261.4</v>
       </c>
       <c r="M66">
-        <v>13955.3910144</v>
+        <v>14173.443999</v>
       </c>
       <c r="N66">
-        <v>-12693.9910144</v>
+        <v>-12912.043999</v>
       </c>
       <c r="O66">
-        <v>-3165.88135899136</v>
+        <v>-3220.2637733506</v>
       </c>
       <c r="P66">
-        <v>-9528.10965540864</v>
+        <v>-9691.780225649401</v>
       </c>
       <c r="Q66">
-        <v>-9505.809655408641</v>
+        <v>-9669.480225649402</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1664184296741691</v>
+        <v>0.1698646705220025</v>
       </c>
       <c r="T66">
-        <v>2.785645027117069</v>
+        <v>2.8652348850347</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.02254276929076255</v>
+        <v>0.02219595745552005</v>
       </c>
       <c r="W66">
-        <v>0.2304844150012382</v>
+        <v>0.2305661932319884</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.09038800838316985</v>
+        <v>0.08899742363881336</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2093206602834933</v>
+        <v>0.2112206602834933</v>
       </c>
       <c r="C67">
-        <v>-31554.67057223959</v>
+        <v>-32747.3112629684</v>
       </c>
       <c r="D67">
-        <v>23324.6344277604</v>
+        <v>23056.73073703159</v>
       </c>
       <c r="E67">
-        <v>58040.105</v>
+        <v>58964.842</v>
       </c>
       <c r="F67">
-        <v>60107.905</v>
+        <v>61032.642</v>
       </c>
       <c r="G67">
         <v>5228.6</v>
@@ -6781,37 +6781,37 @@
         <v>1261.4</v>
       </c>
       <c r="M67">
-        <v>14173.443999</v>
+        <v>14391.4969836</v>
       </c>
       <c r="N67">
-        <v>-12912.043999</v>
+        <v>-13130.0969836</v>
       </c>
       <c r="O67">
-        <v>-3220.2637733506</v>
+        <v>-3274.64618770984</v>
       </c>
       <c r="P67">
-        <v>-9691.780225649401</v>
+        <v>-9855.450795890159</v>
       </c>
       <c r="Q67">
-        <v>-9669.480225649402</v>
+        <v>-9833.15079589016</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1698646705220025</v>
+        <v>0.1735136314197085</v>
       </c>
       <c r="T67">
-        <v>2.8652348850347</v>
+        <v>2.949506499300426</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.02219595745552005</v>
+        <v>0.02185965506983036</v>
       </c>
       <c r="W67">
-        <v>0.2305661932319884</v>
+        <v>0.230645493334534</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.08899742363881336</v>
+        <v>0.08764897782610404</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2112206602834933</v>
+        <v>0.2131206602834933</v>
       </c>
       <c r="C68">
-        <v>-32747.3112629684</v>
+        <v>-33933.86762422443</v>
       </c>
       <c r="D68">
-        <v>23056.73073703159</v>
+        <v>22794.91137577557</v>
       </c>
       <c r="E68">
-        <v>58964.842</v>
+        <v>59889.579</v>
       </c>
       <c r="F68">
-        <v>61032.642</v>
+        <v>61957.379</v>
       </c>
       <c r="G68">
         <v>5228.6</v>
@@ -6863,37 +6863,37 @@
         <v>1261.4</v>
       </c>
       <c r="M68">
-        <v>14391.4969836</v>
+        <v>14609.5499682</v>
       </c>
       <c r="N68">
-        <v>-13130.0969836</v>
+        <v>-13348.1499682</v>
       </c>
       <c r="O68">
-        <v>-3274.64618770984</v>
+        <v>-3329.028602069081</v>
       </c>
       <c r="P68">
-        <v>-9855.450795890159</v>
+        <v>-10019.12136613092</v>
       </c>
       <c r="Q68">
-        <v>-9833.15079589016</v>
+        <v>-9996.821366130922</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1735136314197085</v>
+        <v>0.1773837414627299</v>
       </c>
       <c r="T68">
-        <v>2.949506499300426</v>
+        <v>3.038885484127712</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.02185965506983036</v>
+        <v>0.02153339156132543</v>
       </c>
       <c r="W68">
-        <v>0.230645493334534</v>
+        <v>0.2307224262698395</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.08764897782610404</v>
+        <v>0.08634078412720692</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2131206602834933</v>
+        <v>0.2150206602834933</v>
       </c>
       <c r="C69">
-        <v>-33933.86762422443</v>
+        <v>-35114.54459952896</v>
       </c>
       <c r="D69">
-        <v>22794.91137577557</v>
+        <v>22538.97140047104</v>
       </c>
       <c r="E69">
-        <v>59889.579</v>
+        <v>60814.316</v>
       </c>
       <c r="F69">
-        <v>61957.379</v>
+        <v>62882.116</v>
       </c>
       <c r="G69">
         <v>5228.6</v>
@@ -6945,37 +6945,37 @@
         <v>1261.4</v>
       </c>
       <c r="M69">
-        <v>14609.5499682</v>
+        <v>14827.6029528</v>
       </c>
       <c r="N69">
-        <v>-13348.1499682</v>
+        <v>-13566.2029528</v>
       </c>
       <c r="O69">
-        <v>-3329.028602069081</v>
+        <v>-3383.411016428321</v>
       </c>
       <c r="P69">
-        <v>-10019.12136613092</v>
+        <v>-10182.79193637168</v>
       </c>
       <c r="Q69">
-        <v>-9996.821366130922</v>
+        <v>-10160.49193637168</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1773837414627299</v>
+        <v>0.1814957333834403</v>
       </c>
       <c r="T69">
-        <v>3.038885484127712</v>
+        <v>3.133850655506703</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.02153339156132543</v>
+        <v>0.02121672403836476</v>
       </c>
       <c r="W69">
-        <v>0.2307224262698395</v>
+        <v>0.2307970964717536</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.08634078412720692</v>
+        <v>0.08507106671357156</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2150206602834933</v>
+        <v>0.2169206602834934</v>
       </c>
       <c r="C70">
-        <v>-35114.54459952896</v>
+        <v>-36289.53803022501</v>
       </c>
       <c r="D70">
-        <v>22538.97140047104</v>
+        <v>22288.714969775</v>
       </c>
       <c r="E70">
-        <v>60814.316</v>
+        <v>61739.053</v>
       </c>
       <c r="F70">
-        <v>62882.116</v>
+        <v>63806.853</v>
       </c>
       <c r="G70">
         <v>5228.6</v>
@@ -7027,37 +7027,37 @@
         <v>1261.4</v>
       </c>
       <c r="M70">
-        <v>14827.6029528</v>
+        <v>15045.6559374</v>
       </c>
       <c r="N70">
-        <v>-13566.2029528</v>
+        <v>-13784.2559374</v>
       </c>
       <c r="O70">
-        <v>-3383.411016428321</v>
+        <v>-3437.79343078756</v>
       </c>
       <c r="P70">
-        <v>-10182.79193637168</v>
+        <v>-10346.46250661244</v>
       </c>
       <c r="Q70">
-        <v>-10160.49193637168</v>
+        <v>-10324.16250661244</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1814957333834403</v>
+        <v>0.1858730151054867</v>
       </c>
       <c r="T70">
-        <v>3.133850655506703</v>
+        <v>3.234942612135952</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.02121672403836476</v>
+        <v>0.02090923528418556</v>
       </c>
       <c r="W70">
-        <v>0.2307970964717536</v>
+        <v>0.2308696023199891</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.08507106671357156</v>
+        <v>0.08383815270322992</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2169206602834934</v>
+        <v>0.2188206602834933</v>
       </c>
       <c r="C71">
-        <v>-36289.53803022501</v>
+        <v>-37459.03515524812</v>
       </c>
       <c r="D71">
-        <v>22288.714969775</v>
+        <v>22043.95484475188</v>
       </c>
       <c r="E71">
-        <v>61739.053</v>
+        <v>62663.79</v>
       </c>
       <c r="F71">
-        <v>63806.853</v>
+        <v>64731.59</v>
       </c>
       <c r="G71">
         <v>5228.6</v>
@@ -7109,37 +7109,37 @@
         <v>1261.4</v>
       </c>
       <c r="M71">
-        <v>15045.6559374</v>
+        <v>15263.708922</v>
       </c>
       <c r="N71">
-        <v>-13784.2559374</v>
+        <v>-14002.308922</v>
       </c>
       <c r="O71">
-        <v>-3437.79343078756</v>
+        <v>-3492.175845146801</v>
       </c>
       <c r="P71">
-        <v>-10346.46250661244</v>
+        <v>-10510.1330768532</v>
       </c>
       <c r="Q71">
-        <v>-10324.16250661244</v>
+        <v>-10487.8330768532</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1858730151054867</v>
+        <v>0.1905421156090029</v>
       </c>
       <c r="T71">
-        <v>3.234942612135952</v>
+        <v>3.342774032540484</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.02090923528418556</v>
+        <v>0.02061053192298291</v>
       </c>
       <c r="W71">
-        <v>0.2308696023199891</v>
+        <v>0.2309400365725607</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.08383815270322992</v>
+        <v>0.08264046480746956</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2188206602834933</v>
+        <v>0.2207206602834933</v>
       </c>
       <c r="C72">
-        <v>-37459.03515524812</v>
+        <v>-38623.21507832622</v>
       </c>
       <c r="D72">
-        <v>22043.95484475188</v>
+        <v>21804.51192167379</v>
       </c>
       <c r="E72">
-        <v>62663.79</v>
+        <v>63588.527</v>
       </c>
       <c r="F72">
-        <v>64731.59</v>
+        <v>65656.327</v>
       </c>
       <c r="G72">
         <v>5228.6</v>
@@ -7191,37 +7191,37 @@
         <v>1261.4</v>
       </c>
       <c r="M72">
-        <v>15263.708922</v>
+        <v>15481.7619066</v>
       </c>
       <c r="N72">
-        <v>-14002.308922</v>
+        <v>-14220.3619066</v>
       </c>
       <c r="O72">
-        <v>-3492.175845146801</v>
+        <v>-3546.558259506041</v>
       </c>
       <c r="P72">
-        <v>-10510.1330768532</v>
+        <v>-10673.80364709396</v>
       </c>
       <c r="Q72">
-        <v>-10487.8330768532</v>
+        <v>-10651.50364709396</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1905421156090029</v>
+        <v>0.1955332230437962</v>
       </c>
       <c r="T72">
-        <v>3.342774032540484</v>
+        <v>3.458042102628087</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.02061053192298291</v>
+        <v>0.02032024274096906</v>
       </c>
       <c r="W72">
-        <v>0.2309400365725607</v>
+        <v>0.2310084867616795</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.08264046480746956</v>
+        <v>0.08147651459891359</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2207206602834933</v>
+        <v>0.2226206602834933</v>
       </c>
       <c r="C73">
-        <v>-38623.21507832618</v>
+        <v>-39782.24920505764</v>
       </c>
       <c r="D73">
-        <v>21804.51192167381</v>
+        <v>21570.21479494236</v>
       </c>
       <c r="E73">
-        <v>63588.52699999999</v>
+        <v>64513.264</v>
       </c>
       <c r="F73">
-        <v>65656.32699999999</v>
+        <v>66581.064</v>
       </c>
       <c r="G73">
         <v>5228.6</v>
@@ -7273,37 +7273,37 @@
         <v>1261.4</v>
       </c>
       <c r="M73">
-        <v>15481.7619066</v>
+        <v>15699.8148912</v>
       </c>
       <c r="N73">
-        <v>-14220.3619066</v>
+        <v>-14438.4148912</v>
       </c>
       <c r="O73">
-        <v>-3546.55825950604</v>
+        <v>-3600.94067386528</v>
       </c>
       <c r="P73">
-        <v>-10673.80364709396</v>
+        <v>-10837.47421733472</v>
       </c>
       <c r="Q73">
-        <v>-10651.50364709396</v>
+        <v>-10815.17421733472</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1955332230437961</v>
+        <v>0.2008808381525031</v>
       </c>
       <c r="T73">
-        <v>3.458042102628085</v>
+        <v>3.581543606293374</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.02032024274096907</v>
+        <v>0.02003801714734449</v>
       </c>
       <c r="W73">
-        <v>0.2310084867616795</v>
+        <v>0.2310750355566562</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.08147651459891359</v>
+        <v>0.08034489634059538</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2226206602834933</v>
+        <v>0.2245206602834933</v>
       </c>
       <c r="C74">
-        <v>-39782.24920505764</v>
+        <v>-40936.30165210993</v>
       </c>
       <c r="D74">
-        <v>21570.21479494236</v>
+        <v>21340.89934789006</v>
       </c>
       <c r="E74">
-        <v>64513.264</v>
+        <v>65438.00099999999</v>
       </c>
       <c r="F74">
-        <v>66581.064</v>
+        <v>67505.80099999999</v>
       </c>
       <c r="G74">
         <v>5228.6</v>
@@ -7355,37 +7355,37 @@
         <v>1261.4</v>
       </c>
       <c r="M74">
-        <v>15699.8148912</v>
+        <v>15917.8678758</v>
       </c>
       <c r="N74">
-        <v>-14438.4148912</v>
+        <v>-14656.4678758</v>
       </c>
       <c r="O74">
-        <v>-3600.94067386528</v>
+        <v>-3655.32308822452</v>
       </c>
       <c r="P74">
-        <v>-10837.47421733472</v>
+        <v>-11001.14478757548</v>
       </c>
       <c r="Q74">
-        <v>-10815.17421733472</v>
+        <v>-10978.84478757548</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2008808381525031</v>
+        <v>0.2066245728988921</v>
       </c>
       <c r="T74">
-        <v>3.581543606293374</v>
+        <v>3.714193369489425</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.02003801714734449</v>
+        <v>0.01976352376176443</v>
       </c>
       <c r="W74">
-        <v>0.2310750355566562</v>
+        <v>0.231139761096976</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.08034489634059538</v>
+        <v>0.07924428132223105</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2245206602834933</v>
+        <v>0.2264206602834933</v>
       </c>
       <c r="C75">
-        <v>-40936.30165210993</v>
+        <v>-42085.52963059131</v>
       </c>
       <c r="D75">
-        <v>21340.89934789006</v>
+        <v>21116.40836940869</v>
       </c>
       <c r="E75">
-        <v>65438.00099999999</v>
+        <v>66362.738</v>
       </c>
       <c r="F75">
-        <v>67505.80099999999</v>
+        <v>68430.538</v>
       </c>
       <c r="G75">
         <v>5228.6</v>
@@ -7437,37 +7437,37 @@
         <v>1261.4</v>
       </c>
       <c r="M75">
-        <v>15917.8678758</v>
+        <v>16135.9208604</v>
       </c>
       <c r="N75">
-        <v>-14656.4678758</v>
+        <v>-14874.5208604</v>
       </c>
       <c r="O75">
-        <v>-3655.32308822452</v>
+        <v>-3709.705502583761</v>
       </c>
       <c r="P75">
-        <v>-11001.14478757548</v>
+        <v>-11164.81535781624</v>
       </c>
       <c r="Q75">
-        <v>-10978.84478757548</v>
+        <v>-11142.51535781624</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2066245728988921</v>
+        <v>0.2128101333950033</v>
       </c>
       <c r="T75">
-        <v>3.714193369489425</v>
+        <v>3.857046960623634</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.01976352376176443</v>
+        <v>0.01949644911633518</v>
       </c>
       <c r="W75">
-        <v>0.231139761096976</v>
+        <v>0.2312027372983682</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.07924428132223105</v>
+        <v>0.07817341265571442</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2264206602834933</v>
+        <v>0.2283206602834933</v>
       </c>
       <c r="C76">
-        <v>-42085.52963059131</v>
+        <v>-43230.08380547749</v>
       </c>
       <c r="D76">
-        <v>21116.40836940869</v>
+        <v>20896.59119452251</v>
       </c>
       <c r="E76">
-        <v>66362.738</v>
+        <v>67287.47499999999</v>
       </c>
       <c r="F76">
-        <v>68430.538</v>
+        <v>69355.27499999999</v>
       </c>
       <c r="G76">
         <v>5228.6</v>
@@ -7519,37 +7519,37 @@
         <v>1261.4</v>
       </c>
       <c r="M76">
-        <v>16135.9208604</v>
+        <v>16353.973845</v>
       </c>
       <c r="N76">
-        <v>-14874.5208604</v>
+        <v>-15092.573845</v>
       </c>
       <c r="O76">
-        <v>-3709.705502583761</v>
+        <v>-3764.087916943</v>
       </c>
       <c r="P76">
-        <v>-11164.81535781624</v>
+        <v>-11328.485928057</v>
       </c>
       <c r="Q76">
-        <v>-11142.51535781624</v>
+        <v>-11306.185928057</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2128101333950033</v>
+        <v>0.2194905387308035</v>
       </c>
       <c r="T76">
-        <v>3.857046960623634</v>
+        <v>4.01132883904858</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.01949644911633518</v>
+        <v>0.01923649646145072</v>
       </c>
       <c r="W76">
-        <v>0.2312027372983682</v>
+        <v>0.2312640341343899</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.07817341265571442</v>
+        <v>0.07713110048697158</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2283206602834933</v>
+        <v>0.2302206602834933</v>
       </c>
       <c r="C77">
-        <v>-43230.08380547749</v>
+        <v>-44370.10863282046</v>
       </c>
       <c r="D77">
-        <v>20896.59119452251</v>
+        <v>20681.30336717954</v>
       </c>
       <c r="E77">
-        <v>67287.47499999999</v>
+        <v>68212.212</v>
       </c>
       <c r="F77">
-        <v>69355.27499999999</v>
+        <v>70280.012</v>
       </c>
       <c r="G77">
         <v>5228.6</v>
@@ -7601,37 +7601,37 @@
         <v>1261.4</v>
       </c>
       <c r="M77">
-        <v>16353.973845</v>
+        <v>16572.0268296</v>
       </c>
       <c r="N77">
-        <v>-15092.573845</v>
+        <v>-15310.6268296</v>
       </c>
       <c r="O77">
-        <v>-3764.087916943</v>
+        <v>-3818.47033130224</v>
       </c>
       <c r="P77">
-        <v>-11328.485928057</v>
+        <v>-11492.15649829776</v>
       </c>
       <c r="Q77">
-        <v>-11306.185928057</v>
+        <v>-11469.85649829776</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2194905387308035</v>
+        <v>0.2267276445112536</v>
       </c>
       <c r="T77">
-        <v>4.01132883904858</v>
+        <v>4.178467540675603</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.01923649646145072</v>
+        <v>0.01898338466590531</v>
       </c>
       <c r="W77">
-        <v>0.2312640341343899</v>
+        <v>0.2313237178957795</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.07713110048697158</v>
+        <v>0.07611621758582721</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2302206602834933</v>
+        <v>0.2321206602834933</v>
       </c>
       <c r="C78">
-        <v>-44370.10863282046</v>
+        <v>-45505.74267632522</v>
       </c>
       <c r="D78">
-        <v>20681.30336717954</v>
+        <v>20470.40632367478</v>
       </c>
       <c r="E78">
-        <v>68212.212</v>
+        <v>69136.94899999999</v>
       </c>
       <c r="F78">
-        <v>70280.012</v>
+        <v>71204.749</v>
       </c>
       <c r="G78">
         <v>5228.6</v>
@@ -7683,37 +7683,37 @@
         <v>1261.4</v>
       </c>
       <c r="M78">
-        <v>16572.0268296</v>
+        <v>16790.0798142</v>
       </c>
       <c r="N78">
-        <v>-15310.6268296</v>
+        <v>-15528.6798142</v>
       </c>
       <c r="O78">
-        <v>-3818.47033130224</v>
+        <v>-3872.85274566148</v>
       </c>
       <c r="P78">
-        <v>-11492.15649829776</v>
+        <v>-11655.82706853852</v>
       </c>
       <c r="Q78">
-        <v>-11469.85649829776</v>
+        <v>-11633.52706853852</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2267276445112536</v>
+        <v>0.2345940638378299</v>
       </c>
       <c r="T78">
-        <v>4.178467540675603</v>
+        <v>4.360140042444109</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.01898338466590531</v>
+        <v>0.01873684720271174</v>
       </c>
       <c r="W78">
-        <v>0.2313237178957795</v>
+        <v>0.2313818514296006</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.07611621758582721</v>
+        <v>0.07512769527951779</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2321206602834933</v>
+        <v>0.2340206602834933</v>
       </c>
       <c r="C79">
-        <v>-45505.74267632522</v>
+        <v>-46637.11890475211</v>
       </c>
       <c r="D79">
-        <v>20470.40632367478</v>
+        <v>20263.76709524789</v>
       </c>
       <c r="E79">
-        <v>69136.94899999999</v>
+        <v>70061.686</v>
       </c>
       <c r="F79">
-        <v>71204.749</v>
+        <v>72129.486</v>
       </c>
       <c r="G79">
         <v>5228.6</v>
@@ -7765,37 +7765,37 @@
         <v>1261.4</v>
       </c>
       <c r="M79">
-        <v>16790.0798142</v>
+        <v>17008.1327988</v>
       </c>
       <c r="N79">
-        <v>-15528.6798142</v>
+        <v>-15746.7327988</v>
       </c>
       <c r="O79">
-        <v>-3872.85274566148</v>
+        <v>-3927.235160020721</v>
       </c>
       <c r="P79">
-        <v>-11655.82706853852</v>
+        <v>-11819.49763877928</v>
       </c>
       <c r="Q79">
-        <v>-11633.52706853852</v>
+        <v>-11797.19763877928</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2345940638378299</v>
+        <v>0.2431756121940949</v>
       </c>
       <c r="T79">
-        <v>4.360140042444109</v>
+        <v>4.558328226191568</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.01873684720271174</v>
+        <v>0.01849663121293338</v>
       </c>
       <c r="W79">
-        <v>0.2313818514296006</v>
+        <v>0.2314384943599903</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.07512769527951779</v>
+        <v>0.07416451969901106</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2340206602834933</v>
+        <v>0.2359206602834933</v>
       </c>
       <c r="C80">
-        <v>-46637.11890475211</v>
+        <v>-47764.36497148668</v>
       </c>
       <c r="D80">
-        <v>20263.76709524789</v>
+        <v>20061.25802851332</v>
       </c>
       <c r="E80">
-        <v>70061.686</v>
+        <v>70986.423</v>
       </c>
       <c r="F80">
-        <v>72129.486</v>
+        <v>73054.223</v>
       </c>
       <c r="G80">
         <v>5228.6</v>
@@ -7847,37 +7847,37 @@
         <v>1261.4</v>
       </c>
       <c r="M80">
-        <v>17008.1327988</v>
+        <v>17226.1857834</v>
       </c>
       <c r="N80">
-        <v>-15746.7327988</v>
+        <v>-15964.7857834</v>
       </c>
       <c r="O80">
-        <v>-3927.235160020721</v>
+        <v>-3981.61757437996</v>
       </c>
       <c r="P80">
-        <v>-11819.49763877928</v>
+        <v>-11983.16820902004</v>
       </c>
       <c r="Q80">
-        <v>-11797.19763877928</v>
+        <v>-11960.86820902004</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2431756121940949</v>
+        <v>0.2525744508700041</v>
       </c>
       <c r="T80">
-        <v>4.558328226191568</v>
+        <v>4.775391475057833</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.01849663121293338</v>
+        <v>0.01826249664061777</v>
       </c>
       <c r="W80">
-        <v>0.2314384943599903</v>
+        <v>0.2314937032921423</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.07416451969901106</v>
+        <v>0.07322572831041607</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2359206602834933</v>
+        <v>0.2378206602834933</v>
       </c>
       <c r="C81">
-        <v>-47764.36497148668</v>
+        <v>-48887.60347751162</v>
       </c>
       <c r="D81">
-        <v>20061.25802851332</v>
+        <v>19862.75652248839</v>
       </c>
       <c r="E81">
-        <v>70986.423</v>
+        <v>71911.16</v>
       </c>
       <c r="F81">
-        <v>73054.223</v>
+        <v>73978.96000000001</v>
       </c>
       <c r="G81">
         <v>5228.6</v>
@@ -7929,37 +7929,37 @@
         <v>1261.4</v>
       </c>
       <c r="M81">
-        <v>17226.1857834</v>
+        <v>17444.238768</v>
       </c>
       <c r="N81">
-        <v>-15964.7857834</v>
+        <v>-16182.838768</v>
       </c>
       <c r="O81">
-        <v>-3981.61757437996</v>
+        <v>-4035.999988739201</v>
       </c>
       <c r="P81">
-        <v>-11983.16820902004</v>
+        <v>-12146.8387792608</v>
       </c>
       <c r="Q81">
-        <v>-11960.86820902004</v>
+        <v>-12124.5387792608</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2525744508700041</v>
+        <v>0.2629131734135044</v>
       </c>
       <c r="T81">
-        <v>4.775391475057833</v>
+        <v>5.014161048810725</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.01826249664061777</v>
+        <v>0.01803421543261004</v>
       </c>
       <c r="W81">
-        <v>0.2314937032921423</v>
+        <v>0.2315475320009905</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.07322572831041607</v>
+        <v>0.07231040670653588</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2378206602834933</v>
+        <v>0.2397206602834933</v>
       </c>
       <c r="C82">
-        <v>-48887.60347751162</v>
+        <v>-50006.95221891947</v>
       </c>
       <c r="D82">
-        <v>19862.75652248839</v>
+        <v>19668.14478108053</v>
       </c>
       <c r="E82">
-        <v>71911.16</v>
+        <v>72835.897</v>
       </c>
       <c r="F82">
-        <v>73978.96000000001</v>
+        <v>74903.697</v>
       </c>
       <c r="G82">
         <v>5228.6</v>
@@ -8011,37 +8011,37 @@
         <v>1261.4</v>
       </c>
       <c r="M82">
-        <v>17444.238768</v>
+        <v>17662.2917526</v>
       </c>
       <c r="N82">
-        <v>-16182.838768</v>
+        <v>-16400.8917526</v>
       </c>
       <c r="O82">
-        <v>-4035.999988739201</v>
+        <v>-4090.38240309844</v>
       </c>
       <c r="P82">
-        <v>-12146.8387792608</v>
+        <v>-12310.50934950156</v>
       </c>
       <c r="Q82">
-        <v>-12124.5387792608</v>
+        <v>-12288.20934950156</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2629131734135044</v>
+        <v>0.2743401825405309</v>
       </c>
       <c r="T82">
-        <v>5.014161048810725</v>
+        <v>5.278064261906026</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.01803421543261004</v>
+        <v>0.01781157079763955</v>
       </c>
       <c r="W82">
-        <v>0.2315475320009905</v>
+        <v>0.2316000316059166</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.07231040670653588</v>
+        <v>0.07141768563608486</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2397206602834933</v>
+        <v>0.2416206602834933</v>
       </c>
       <c r="C83">
-        <v>-50006.95221891947</v>
+        <v>-51122.52442001599</v>
       </c>
       <c r="D83">
-        <v>19668.14478108053</v>
+        <v>19477.30957998402</v>
       </c>
       <c r="E83">
-        <v>72835.897</v>
+        <v>73760.63400000001</v>
       </c>
       <c r="F83">
-        <v>74903.697</v>
+        <v>75828.43400000001</v>
       </c>
       <c r="G83">
         <v>5228.6</v>
@@ -8093,37 +8093,37 @@
         <v>1261.4</v>
       </c>
       <c r="M83">
-        <v>17662.2917526</v>
+        <v>17880.3447372</v>
       </c>
       <c r="N83">
-        <v>-16400.8917526</v>
+        <v>-16618.9447372</v>
       </c>
       <c r="O83">
-        <v>-4090.38240309844</v>
+        <v>-4144.76481745768</v>
       </c>
       <c r="P83">
-        <v>-12310.50934950156</v>
+        <v>-12474.17991974232</v>
       </c>
       <c r="Q83">
-        <v>-12288.20934950156</v>
+        <v>-12451.87991974232</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2743401825405309</v>
+        <v>0.2870368593483382</v>
       </c>
       <c r="T83">
-        <v>5.278064261906026</v>
+        <v>5.571290054234139</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.01781157079763955</v>
+        <v>0.01759435651961956</v>
       </c>
       <c r="W83">
-        <v>0.2316000316059166</v>
+        <v>0.2316512507326737</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.07141768563608486</v>
+        <v>0.07054673825027902</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2416206602834933</v>
+        <v>0.2435206602834933</v>
       </c>
       <c r="C84">
-        <v>-51122.52442001599</v>
+        <v>-52234.4289529835</v>
       </c>
       <c r="D84">
-        <v>19477.30957998402</v>
+        <v>19290.1420470165</v>
       </c>
       <c r="E84">
-        <v>73760.63400000001</v>
+        <v>74685.371</v>
       </c>
       <c r="F84">
-        <v>75828.43400000001</v>
+        <v>76753.171</v>
       </c>
       <c r="G84">
         <v>5228.6</v>
@@ -8175,37 +8175,37 @@
         <v>1261.4</v>
       </c>
       <c r="M84">
-        <v>17880.3447372</v>
+        <v>18098.3977218</v>
       </c>
       <c r="N84">
-        <v>-16618.9447372</v>
+        <v>-16836.9977218</v>
       </c>
       <c r="O84">
-        <v>-4144.76481745768</v>
+        <v>-4199.14723181692</v>
       </c>
       <c r="P84">
-        <v>-12474.17991974232</v>
+        <v>-12637.85048998308</v>
       </c>
       <c r="Q84">
-        <v>-12451.87991974232</v>
+        <v>-12615.55048998308</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2870368593483382</v>
+        <v>0.301227262839417</v>
       </c>
       <c r="T84">
-        <v>5.571290054234139</v>
+        <v>5.899012998600854</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.01759435651961956</v>
+        <v>0.017382376320588</v>
       </c>
       <c r="W84">
-        <v>0.2316512507326737</v>
+        <v>0.2317012356636053</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.07054673825027902</v>
+        <v>0.06969677754846837</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2435206602834933</v>
+        <v>0.2454206602834934</v>
       </c>
       <c r="C85">
-        <v>-52234.4289529835</v>
+        <v>-53342.77054499957</v>
       </c>
       <c r="D85">
-        <v>19290.1420470165</v>
+        <v>19106.53745500044</v>
       </c>
       <c r="E85">
-        <v>74685.371</v>
+        <v>75610.10800000001</v>
       </c>
       <c r="F85">
-        <v>76753.171</v>
+        <v>77677.90800000001</v>
       </c>
       <c r="G85">
         <v>5228.6</v>
@@ -8257,37 +8257,37 @@
         <v>1261.4</v>
       </c>
       <c r="M85">
-        <v>18098.3977218</v>
+        <v>18316.4507064</v>
       </c>
       <c r="N85">
-        <v>-16836.9977218</v>
+        <v>-17055.0507064</v>
       </c>
       <c r="O85">
-        <v>-4199.14723181692</v>
+        <v>-4253.529646176161</v>
       </c>
       <c r="P85">
-        <v>-12637.85048998308</v>
+        <v>-12801.52106022384</v>
       </c>
       <c r="Q85">
-        <v>-12615.55048998308</v>
+        <v>-12779.22106022384</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.301227262839417</v>
+        <v>0.3171914667668806</v>
       </c>
       <c r="T85">
-        <v>5.899012998600854</v>
+        <v>6.267701311013409</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.017382376320588</v>
+        <v>0.01717544326915242</v>
       </c>
       <c r="W85">
-        <v>0.2317012356636053</v>
+        <v>0.2317500304771339</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.06969677754846837</v>
+        <v>0.06886705400622473</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2454206602834933</v>
+        <v>0.2473206602834933</v>
       </c>
       <c r="C86">
-        <v>-53342.77054499957</v>
+        <v>-54447.64997363904</v>
       </c>
       <c r="D86">
-        <v>19106.53745500043</v>
+        <v>18926.39502636095</v>
       </c>
       <c r="E86">
-        <v>75610.10799999999</v>
+        <v>76534.84499999999</v>
       </c>
       <c r="F86">
-        <v>77677.908</v>
+        <v>78602.64499999999</v>
       </c>
       <c r="G86">
         <v>5228.6</v>
@@ -8339,37 +8339,37 @@
         <v>1261.4</v>
       </c>
       <c r="M86">
-        <v>18316.4507064</v>
+        <v>18534.503691</v>
       </c>
       <c r="N86">
-        <v>-17055.0507064</v>
+        <v>-17273.103691</v>
       </c>
       <c r="O86">
-        <v>-4253.52964617616</v>
+        <v>-4307.912060535399</v>
       </c>
       <c r="P86">
-        <v>-12801.52106022384</v>
+        <v>-12965.1916304646</v>
       </c>
       <c r="Q86">
-        <v>-12779.22106022384</v>
+        <v>-12942.8916304646</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3171914667668804</v>
+        <v>0.3352842312180058</v>
       </c>
       <c r="T86">
-        <v>6.267701311013405</v>
+        <v>6.685548065080965</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.01717544326915242</v>
+        <v>0.01697337923069181</v>
       </c>
       <c r="W86">
-        <v>0.2317500304771339</v>
+        <v>0.2317976771774029</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.06886705400622473</v>
+        <v>0.06805685337085732</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2473206602834933</v>
+        <v>0.2492206602834933</v>
       </c>
       <c r="C87">
-        <v>-54447.64997363904</v>
+        <v>-55549.16425132544</v>
       </c>
       <c r="D87">
-        <v>18926.39502636095</v>
+        <v>18749.61774867455</v>
       </c>
       <c r="E87">
-        <v>76534.84499999999</v>
+        <v>77459.58199999999</v>
       </c>
       <c r="F87">
-        <v>78602.64499999999</v>
+        <v>79527.382</v>
       </c>
       <c r="G87">
         <v>5228.6</v>
@@ -8421,37 +8421,37 @@
         <v>1261.4</v>
       </c>
       <c r="M87">
-        <v>18534.503691</v>
+        <v>18752.5566756</v>
       </c>
       <c r="N87">
-        <v>-17273.103691</v>
+        <v>-17491.1566756</v>
       </c>
       <c r="O87">
-        <v>-4307.912060535399</v>
+        <v>-4362.29447489464</v>
       </c>
       <c r="P87">
-        <v>-12965.1916304646</v>
+        <v>-13128.86220070536</v>
       </c>
       <c r="Q87">
-        <v>-12942.8916304646</v>
+        <v>-13106.56220070536</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3352842312180058</v>
+        <v>0.3559616763050062</v>
       </c>
       <c r="T87">
-        <v>6.685548065080965</v>
+        <v>7.163087212586748</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.01697337923069181</v>
+        <v>0.01677601435591632</v>
       </c>
       <c r="W87">
-        <v>0.2317976771774029</v>
+        <v>0.2318442158148749</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.06805685337085732</v>
+        <v>0.06726549461073106</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2492206602834933</v>
+        <v>0.2511206602834933</v>
       </c>
       <c r="C88">
-        <v>-55549.16425132544</v>
+        <v>-56647.40679954106</v>
       </c>
       <c r="D88">
-        <v>18749.61774867455</v>
+        <v>18576.11220045893</v>
       </c>
       <c r="E88">
-        <v>77459.58199999999</v>
+        <v>78384.31899999999</v>
       </c>
       <c r="F88">
-        <v>79527.382</v>
+        <v>80452.11899999999</v>
       </c>
       <c r="G88">
         <v>5228.6</v>
@@ -8503,37 +8503,37 @@
         <v>1261.4</v>
       </c>
       <c r="M88">
-        <v>18752.5566756</v>
+        <v>18970.6096602</v>
       </c>
       <c r="N88">
-        <v>-17491.1566756</v>
+        <v>-17709.2096602</v>
       </c>
       <c r="O88">
-        <v>-4362.29447489464</v>
+        <v>-4416.676889253879</v>
       </c>
       <c r="P88">
-        <v>-13128.86220070536</v>
+        <v>-13292.53277094612</v>
       </c>
       <c r="Q88">
-        <v>-13106.56220070536</v>
+        <v>-13270.23277094612</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3559616763050062</v>
+        <v>0.3798202667900066</v>
       </c>
       <c r="T88">
-        <v>7.163087212586748</v>
+        <v>7.714093921247267</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.01677601435591632</v>
+        <v>0.01658318660469889</v>
       </c>
       <c r="W88">
-        <v>0.2318442158148749</v>
+        <v>0.231889684598612</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.06726549461073106</v>
+        <v>0.06649232800601002</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2511206602834933</v>
+        <v>0.2530206602834933</v>
       </c>
       <c r="C89">
-        <v>-56647.40679954106</v>
+        <v>-57742.46761345318</v>
       </c>
       <c r="D89">
-        <v>18576.11220045893</v>
+        <v>18405.78838654681</v>
       </c>
       <c r="E89">
-        <v>78384.31899999999</v>
+        <v>79309.056</v>
       </c>
       <c r="F89">
-        <v>80452.11899999999</v>
+        <v>81376.856</v>
       </c>
       <c r="G89">
         <v>5228.6</v>
@@ -8585,37 +8585,37 @@
         <v>1261.4</v>
       </c>
       <c r="M89">
-        <v>18970.6096602</v>
+        <v>19188.6626448</v>
       </c>
       <c r="N89">
-        <v>-17709.2096602</v>
+        <v>-17927.2626448</v>
       </c>
       <c r="O89">
-        <v>-4416.676889253879</v>
+        <v>-4471.05930361312</v>
       </c>
       <c r="P89">
-        <v>-13292.53277094612</v>
+        <v>-13456.20334118688</v>
       </c>
       <c r="Q89">
-        <v>-13270.23277094612</v>
+        <v>-13433.90334118688</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3798202667900066</v>
+        <v>0.4076552890225073</v>
       </c>
       <c r="T89">
-        <v>7.714093921247267</v>
+        <v>8.356935081351208</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.01658318660469889</v>
+        <v>0.01639474130237277</v>
       </c>
       <c r="W89">
-        <v>0.231889684598612</v>
+        <v>0.2319341200009005</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.06649232800601002</v>
+        <v>0.06573673336957808</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2530206602834933</v>
+        <v>0.2549206602834934</v>
       </c>
       <c r="C90">
-        <v>-57742.46761345318</v>
+        <v>-58834.43341756576</v>
       </c>
       <c r="D90">
-        <v>18405.78838654681</v>
+        <v>18238.55958243424</v>
       </c>
       <c r="E90">
-        <v>79309.056</v>
+        <v>80233.79299999999</v>
       </c>
       <c r="F90">
-        <v>81376.856</v>
+        <v>82301.59299999999</v>
       </c>
       <c r="G90">
         <v>5228.6</v>
@@ -8667,37 +8667,37 @@
         <v>1261.4</v>
       </c>
       <c r="M90">
-        <v>19188.6626448</v>
+        <v>19406.7156294</v>
       </c>
       <c r="N90">
-        <v>-17927.2626448</v>
+        <v>-18145.3156294</v>
       </c>
       <c r="O90">
-        <v>-4471.05930361312</v>
+        <v>-4525.44171797236</v>
       </c>
       <c r="P90">
-        <v>-13456.20334118688</v>
+        <v>-13619.87391142764</v>
       </c>
       <c r="Q90">
-        <v>-13433.90334118688</v>
+        <v>-13597.57391142764</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4076552890225073</v>
+        <v>0.4405512243881898</v>
       </c>
       <c r="T90">
-        <v>8.356935081351208</v>
+        <v>9.116656452383136</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.01639474130237277</v>
+        <v>0.01621053072594162</v>
       </c>
       <c r="W90">
-        <v>0.2319341200009005</v>
+        <v>0.231977556854823</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.06573673336957808</v>
+        <v>0.06499811838789749</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2549206602834934</v>
+        <v>0.2568206602834933</v>
       </c>
       <c r="C91">
-        <v>-58834.43341756576</v>
+        <v>-59923.38781296235</v>
       </c>
       <c r="D91">
-        <v>18238.55958243424</v>
+        <v>18074.34218703765</v>
       </c>
       <c r="E91">
-        <v>80233.79299999999</v>
+        <v>81158.53</v>
       </c>
       <c r="F91">
-        <v>82301.59299999999</v>
+        <v>83226.33</v>
       </c>
       <c r="G91">
         <v>5228.6</v>
@@ -8749,37 +8749,37 @@
         <v>1261.4</v>
       </c>
       <c r="M91">
-        <v>19406.7156294</v>
+        <v>19624.768614</v>
       </c>
       <c r="N91">
-        <v>-18145.3156294</v>
+        <v>-18363.368614</v>
       </c>
       <c r="O91">
-        <v>-4525.44171797236</v>
+        <v>-4579.8241323316</v>
       </c>
       <c r="P91">
-        <v>-13619.87391142764</v>
+        <v>-13783.5444816684</v>
       </c>
       <c r="Q91">
-        <v>-13597.57391142764</v>
+        <v>-13761.2444816684</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4405512243881898</v>
+        <v>0.4800263468270088</v>
       </c>
       <c r="T91">
-        <v>9.116656452383136</v>
+        <v>10.02832209762145</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.01621053072594162</v>
+        <v>0.0160304137178756</v>
       </c>
       <c r="W91">
-        <v>0.231977556854823</v>
+        <v>0.2320200284453249</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.06499811838789749</v>
+        <v>0.06427591707247637</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2568206602834933</v>
+        <v>0.2587206602834933</v>
       </c>
       <c r="C92">
-        <v>-59923.38781296235</v>
+        <v>-61009.41141666557</v>
       </c>
       <c r="D92">
-        <v>18074.34218703765</v>
+        <v>17913.05558333443</v>
       </c>
       <c r="E92">
-        <v>81158.53</v>
+        <v>82083.26699999999</v>
       </c>
       <c r="F92">
-        <v>83226.33</v>
+        <v>84151.067</v>
       </c>
       <c r="G92">
         <v>5228.6</v>
@@ -8831,37 +8831,37 @@
         <v>1261.4</v>
       </c>
       <c r="M92">
-        <v>19624.768614</v>
+        <v>19842.8215986</v>
       </c>
       <c r="N92">
-        <v>-18363.368614</v>
+        <v>-18581.4215986</v>
       </c>
       <c r="O92">
-        <v>-4579.8241323316</v>
+        <v>-4634.20654669084</v>
       </c>
       <c r="P92">
-        <v>-13783.5444816684</v>
+        <v>-13947.21505190916</v>
       </c>
       <c r="Q92">
-        <v>-13761.2444816684</v>
+        <v>-13924.91505190916</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4800263468270088</v>
+        <v>0.5282737186966765</v>
       </c>
       <c r="T92">
-        <v>10.02832209762145</v>
+        <v>11.14258010846828</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0160304137178756</v>
+        <v>0.01585425532537147</v>
       </c>
       <c r="W92">
-        <v>0.2320200284453249</v>
+        <v>0.2320615665942774</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.06427591707247637</v>
+        <v>0.06356958831343817</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2587206602834933</v>
+        <v>0.2606206602834933</v>
       </c>
       <c r="C93">
-        <v>-61009.41141666557</v>
+        <v>-62092.58199360096</v>
       </c>
       <c r="D93">
-        <v>17913.05558333443</v>
+        <v>17754.62200639904</v>
       </c>
       <c r="E93">
-        <v>82083.26699999999</v>
+        <v>83008.004</v>
       </c>
       <c r="F93">
-        <v>84151.067</v>
+        <v>85075.804</v>
       </c>
       <c r="G93">
         <v>5228.6</v>
@@ -8913,37 +8913,37 @@
         <v>1261.4</v>
       </c>
       <c r="M93">
-        <v>19842.8215986</v>
+        <v>20060.8745832</v>
       </c>
       <c r="N93">
-        <v>-18581.4215986</v>
+        <v>-18799.4745832</v>
       </c>
       <c r="O93">
-        <v>-4634.20654669084</v>
+        <v>-4688.588961050081</v>
       </c>
       <c r="P93">
-        <v>-13947.21505190916</v>
+        <v>-14110.88562214992</v>
       </c>
       <c r="Q93">
-        <v>-13924.91505190916</v>
+        <v>-14088.58562214992</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5282737186966765</v>
+        <v>0.5885829335337612</v>
       </c>
       <c r="T93">
-        <v>11.14258010846828</v>
+        <v>12.53540262202682</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.01585425532537147</v>
+        <v>0.01568192646313917</v>
       </c>
       <c r="W93">
-        <v>0.2320615665942774</v>
+        <v>0.2321022017399918</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.06356958831343817</v>
+        <v>0.0628786145274226</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2606206602834933</v>
+        <v>0.2625206602834933</v>
       </c>
       <c r="C94">
-        <v>-62092.58199360096</v>
+        <v>-63172.97458161933</v>
       </c>
       <c r="D94">
-        <v>17754.62200639904</v>
+        <v>17598.96641838066</v>
       </c>
       <c r="E94">
-        <v>83008.004</v>
+        <v>83932.74099999999</v>
       </c>
       <c r="F94">
-        <v>85075.804</v>
+        <v>86000.541</v>
       </c>
       <c r="G94">
         <v>5228.6</v>
@@ -8995,37 +8995,37 @@
         <v>1261.4</v>
       </c>
       <c r="M94">
-        <v>20060.8745832</v>
+        <v>20278.9275678</v>
       </c>
       <c r="N94">
-        <v>-18799.4745832</v>
+        <v>-19017.5275678</v>
       </c>
       <c r="O94">
-        <v>-4688.588961050081</v>
+        <v>-4742.97137540932</v>
       </c>
       <c r="P94">
-        <v>-14110.88562214992</v>
+        <v>-14274.55619239068</v>
       </c>
       <c r="Q94">
-        <v>-14088.58562214992</v>
+        <v>-14252.25619239068</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5885829335337612</v>
+        <v>0.6661233526100128</v>
       </c>
       <c r="T94">
-        <v>12.53540262202682</v>
+        <v>14.32617442517351</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.01568192646313917</v>
+        <v>0.01551330359794412</v>
       </c>
       <c r="W94">
-        <v>0.2321022017399918</v>
+        <v>0.2321419630116048</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.0628786145274226</v>
+        <v>0.06220250039271913</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2625206602834933</v>
+        <v>0.2644206602834933</v>
       </c>
       <c r="C95">
-        <v>-63172.97458161933</v>
+        <v>-64250.66160999984</v>
       </c>
       <c r="D95">
-        <v>17598.96641838066</v>
+        <v>17446.01639000017</v>
       </c>
       <c r="E95">
-        <v>83932.74099999999</v>
+        <v>84857.478</v>
       </c>
       <c r="F95">
-        <v>86000.541</v>
+        <v>86925.27800000001</v>
       </c>
       <c r="G95">
         <v>5228.6</v>
@@ -9077,37 +9077,37 @@
         <v>1261.4</v>
       </c>
       <c r="M95">
-        <v>20278.9275678</v>
+        <v>20496.9805524</v>
       </c>
       <c r="N95">
-        <v>-19017.5275678</v>
+        <v>-19235.5805524</v>
       </c>
       <c r="O95">
-        <v>-4742.97137540932</v>
+        <v>-4797.353789768561</v>
       </c>
       <c r="P95">
-        <v>-14274.55619239068</v>
+        <v>-14438.22676263144</v>
       </c>
       <c r="Q95">
-        <v>-14252.25619239068</v>
+        <v>-14415.92676263144</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6661233526100128</v>
+        <v>0.769510578045015</v>
       </c>
       <c r="T95">
-        <v>14.32617442517351</v>
+        <v>16.71387016270243</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.01551330359794412</v>
+        <v>0.01534826845328514</v>
       </c>
       <c r="W95">
-        <v>0.2321419630116048</v>
+        <v>0.2321808782987154</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.06220250039271913</v>
+        <v>0.06154077166513694</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2644206602834933</v>
+        <v>0.2663206602834933</v>
       </c>
       <c r="C96">
-        <v>-64250.66160999984</v>
+        <v>-65325.7130118268</v>
       </c>
       <c r="D96">
-        <v>17446.01639000017</v>
+        <v>17295.7019881732</v>
       </c>
       <c r="E96">
-        <v>84857.478</v>
+        <v>85782.215</v>
       </c>
       <c r="F96">
-        <v>86925.27800000001</v>
+        <v>87850.015</v>
       </c>
       <c r="G96">
         <v>5228.6</v>
@@ -9159,37 +9159,37 @@
         <v>1261.4</v>
       </c>
       <c r="M96">
-        <v>20496.9805524</v>
+        <v>20715.033537</v>
       </c>
       <c r="N96">
-        <v>-19235.5805524</v>
+        <v>-19453.633537</v>
       </c>
       <c r="O96">
-        <v>-4797.353789768561</v>
+        <v>-4851.736204127799</v>
       </c>
       <c r="P96">
-        <v>-14438.22676263144</v>
+        <v>-14601.8973328722</v>
       </c>
       <c r="Q96">
-        <v>-14415.92676263144</v>
+        <v>-14579.5973328722</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.769510578045015</v>
+        <v>0.9142526936540185</v>
       </c>
       <c r="T96">
-        <v>16.71387016270243</v>
+        <v>20.05664419524292</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.01534826845328514</v>
+        <v>0.01518670773272425</v>
       </c>
       <c r="W96">
-        <v>0.2321808782987154</v>
+        <v>0.2322189743166236</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.06154077166513694</v>
+        <v>0.0608929740686619</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2663206602834933</v>
+        <v>0.2682206602834933</v>
       </c>
       <c r="C97">
-        <v>-65325.7130118268</v>
+        <v>-66398.19633060691</v>
       </c>
       <c r="D97">
-        <v>17295.7019881732</v>
+        <v>17147.95566939309</v>
       </c>
       <c r="E97">
-        <v>85782.215</v>
+        <v>86706.952</v>
       </c>
       <c r="F97">
-        <v>87850.015</v>
+        <v>88774.75200000001</v>
       </c>
       <c r="G97">
         <v>5228.6</v>
@@ -9241,37 +9241,37 @@
         <v>1261.4</v>
       </c>
       <c r="M97">
-        <v>20715.033537</v>
+        <v>20933.0865216</v>
       </c>
       <c r="N97">
-        <v>-19453.633537</v>
+        <v>-19671.6865216</v>
       </c>
       <c r="O97">
-        <v>-4851.736204127799</v>
+        <v>-4906.11861848704</v>
       </c>
       <c r="P97">
-        <v>-14601.8973328722</v>
+        <v>-14765.56790311296</v>
       </c>
       <c r="Q97">
-        <v>-14579.5973328722</v>
+        <v>-14743.26790311296</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9142526936540185</v>
+        <v>1.131365867067524</v>
       </c>
       <c r="T97">
-        <v>20.05664419524292</v>
+        <v>25.07080524405367</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.01518670773272425</v>
+        <v>0.01502851286050837</v>
       </c>
       <c r="W97">
-        <v>0.2322189743166236</v>
+        <v>0.2322562766674922</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.0608929740686619</v>
+        <v>0.06025867225544657</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2682206602834933</v>
+        <v>0.2701206602834933</v>
       </c>
       <c r="C98">
-        <v>-66398.19633060691</v>
+        <v>-67468.17682146803</v>
       </c>
       <c r="D98">
-        <v>17147.95566939309</v>
+        <v>17002.71217853197</v>
       </c>
       <c r="E98">
-        <v>86706.95199999999</v>
+        <v>87631.689</v>
       </c>
       <c r="F98">
-        <v>88774.75199999999</v>
+        <v>89699.489</v>
       </c>
       <c r="G98">
         <v>5228.6</v>
@@ -9323,37 +9323,37 @@
         <v>1261.4</v>
       </c>
       <c r="M98">
-        <v>20933.0865216</v>
+        <v>21151.1395062</v>
       </c>
       <c r="N98">
-        <v>-19671.6865216</v>
+        <v>-19889.7395062</v>
       </c>
       <c r="O98">
-        <v>-4906.118618487039</v>
+        <v>-4960.50103284628</v>
       </c>
       <c r="P98">
-        <v>-14765.56790311296</v>
+        <v>-14929.23847335372</v>
       </c>
       <c r="Q98">
-        <v>-14743.26790311296</v>
+        <v>-14906.93847335372</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.131365867067521</v>
+        <v>1.493221156090028</v>
       </c>
       <c r="T98">
-        <v>25.0708052440536</v>
+        <v>33.42774032540481</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.01502851286050837</v>
+        <v>0.01487357973823509</v>
       </c>
       <c r="W98">
-        <v>0.2322562766674922</v>
+        <v>0.2322928098977242</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.06025867225544668</v>
+        <v>0.05963744883013278</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2701206602834933</v>
+        <v>0.2720206602834933</v>
       </c>
       <c r="C99">
-        <v>-67468.17682146803</v>
+        <v>-68535.71754725827</v>
       </c>
       <c r="D99">
-        <v>17002.71217853197</v>
+        <v>16859.90845274173</v>
       </c>
       <c r="E99">
-        <v>87631.689</v>
+        <v>88556.42599999999</v>
       </c>
       <c r="F99">
-        <v>89699.489</v>
+        <v>90624.226</v>
       </c>
       <c r="G99">
         <v>5228.6</v>
@@ -9405,37 +9405,37 @@
         <v>1261.4</v>
       </c>
       <c r="M99">
-        <v>21151.1395062</v>
+        <v>21369.1924908</v>
       </c>
       <c r="N99">
-        <v>-19889.7395062</v>
+        <v>-20107.7924908</v>
       </c>
       <c r="O99">
-        <v>-4960.50103284628</v>
+        <v>-5014.88344720552</v>
       </c>
       <c r="P99">
-        <v>-14929.23847335372</v>
+        <v>-15092.90904359448</v>
       </c>
       <c r="Q99">
-        <v>-14906.93847335372</v>
+        <v>-15070.60904359448</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.493221156090028</v>
+        <v>2.216931734135042</v>
       </c>
       <c r="T99">
-        <v>33.42774032540481</v>
+        <v>50.1416104881072</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01487357973823509</v>
+        <v>0.01472180851641636</v>
       </c>
       <c r="W99">
-        <v>0.2322928098977242</v>
+        <v>0.232328597551829</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.05963744883013278</v>
+        <v>0.05902890343390688</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2720206602834933</v>
+        <v>0.2739206602834933</v>
       </c>
       <c r="C100">
-        <v>-68535.71754725827</v>
+        <v>-69600.87946984266</v>
       </c>
       <c r="D100">
-        <v>16859.90845274173</v>
+        <v>16719.48353015734</v>
       </c>
       <c r="E100">
-        <v>88556.42599999999</v>
+        <v>89481.163</v>
       </c>
       <c r="F100">
-        <v>90624.226</v>
+        <v>91548.963</v>
       </c>
       <c r="G100">
         <v>5228.6</v>
@@ -9487,37 +9487,37 @@
         <v>1261.4</v>
       </c>
       <c r="M100">
-        <v>21369.1924908</v>
+        <v>21587.2454754</v>
       </c>
       <c r="N100">
-        <v>-20107.7924908</v>
+        <v>-20325.8454754</v>
       </c>
       <c r="O100">
-        <v>-5014.88344720552</v>
+        <v>-5069.265861564761</v>
       </c>
       <c r="P100">
-        <v>-15092.90904359448</v>
+        <v>-15256.57961383524</v>
       </c>
       <c r="Q100">
-        <v>-15070.60904359448</v>
+        <v>-15234.27961383524</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.216931734135042</v>
+        <v>4.388063468270084</v>
       </c>
       <c r="T100">
-        <v>50.1416104881072</v>
+        <v>100.2832209762144</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.01472180851641636</v>
+        <v>0.0145731033798869</v>
       </c>
       <c r="W100">
-        <v>0.232328597551829</v>
+        <v>0.2323636622230227</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.05902890343390688</v>
+        <v>0.05843265188406943</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2739206602834933</v>
-      </c>
-      <c r="C101">
-        <v>-69600.87946984266</v>
-      </c>
-      <c r="D101">
-        <v>16719.48353015734</v>
-      </c>
-      <c r="E101">
-        <v>89481.163</v>
-      </c>
-      <c r="F101">
-        <v>91548.963</v>
-      </c>
-      <c r="G101">
-        <v>5228.6</v>
-      </c>
-      <c r="H101">
-        <v>90405.89999999999</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1283.7</v>
-      </c>
-      <c r="K101">
-        <v>22.29999999999995</v>
-      </c>
-      <c r="L101">
-        <v>1261.4</v>
-      </c>
-      <c r="M101">
-        <v>21587.2454754</v>
-      </c>
-      <c r="N101">
-        <v>-20325.8454754</v>
-      </c>
-      <c r="O101">
-        <v>-5069.265861564761</v>
-      </c>
-      <c r="P101">
-        <v>-15256.57961383524</v>
-      </c>
-      <c r="Q101">
-        <v>-15234.27961383524</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.388063468270084</v>
-      </c>
-      <c r="T101">
-        <v>100.2832209762144</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.0145731033798869</v>
-      </c>
-      <c r="W101">
-        <v>0.2323636622230227</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.05843265188406943</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
